--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL25" headerRowCount="1">
-  <autoFilter ref="A1:EL25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL26" headerRowCount="1">
+  <autoFilter ref="A1:EL26"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL25"/>
+  <dimension ref="A1:EL26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>1.33</v>
       </c>
       <c r="DE3" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
         <v>1.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -8590,7 +8590,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE17" t="n">
         <v>0.33</v>
@@ -9510,7 +9510,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE19" t="n">
         <v>1</v>
@@ -11329,7 +11329,7 @@
         <v>1.33</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -12350,6 +12350,454 @@
       <c r="EJ25" t="inlineStr"/>
       <c r="EK25" t="inlineStr"/>
       <c r="EL25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46079.95833333334</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO26" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP26" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW26" t="inlineStr"/>
+      <c r="DX26" t="inlineStr"/>
+      <c r="DY26" t="inlineStr"/>
+      <c r="DZ26" t="inlineStr"/>
+      <c r="EA26" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB26" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE26" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EF26" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EJ26" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EK26" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EL26" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL26" headerRowCount="1">
-  <autoFilter ref="A1:EL26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL30" headerRowCount="1">
+  <autoFilter ref="A1:EL30"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL26"/>
+  <dimension ref="A1:EL30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DE2" t="n">
         <v>1.33</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE3" t="n">
         <v>1.75</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE7" t="n">
         <v>2</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DE8" t="n">
         <v>2.33</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -6325,7 +6325,7 @@
         <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6781,7 +6781,7 @@
         <v>2.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DE15" t="n">
         <v>2</v>
@@ -8134,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DE18" t="n">
         <v>1.33</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE22" t="n">
         <v>2.33</v>
@@ -11326,7 +11326,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE23" t="n">
         <v>1.75</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11785,7 +11785,7 @@
         <v>0.33</v>
       </c>
       <c r="DE24" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -12400,7 +12400,7 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -12444,7 +12444,7 @@
         <v>6</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>2.25</v>
@@ -12564,13 +12564,13 @@
         <v>4</v>
       </c>
       <c r="BR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
@@ -12734,70 +12734,1894 @@
       <c r="DV26" t="b">
         <v>0</v>
       </c>
-      <c r="DW26" t="inlineStr"/>
-      <c r="DX26" t="inlineStr"/>
-      <c r="DY26" t="inlineStr"/>
-      <c r="DZ26" t="inlineStr"/>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY26" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ26" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EC26" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="EH26" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EI26" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EK26" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EL26" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
+      <c r="EI26" t="inlineStr"/>
+      <c r="EJ26" t="inlineStr"/>
+      <c r="EK26" t="inlineStr"/>
+      <c r="EL26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46080.95833333334</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11</v>
+      </c>
+      <c r="V27" t="n">
+        <v>4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Luis Tróccoli</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>133</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>17</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW27" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EB27" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EF27" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="EG27" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI27" t="inlineStr"/>
+      <c r="EJ27" t="inlineStr"/>
+      <c r="EK27" t="inlineStr"/>
+      <c r="EL27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46081.53125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>8</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK28" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DN28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW28" t="inlineStr"/>
+      <c r="DX28" t="inlineStr"/>
+      <c r="DY28" t="inlineStr"/>
+      <c r="DZ28" t="inlineStr"/>
+      <c r="EA28" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EB28" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EC28" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="ED28" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE28" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EF28" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="EG28" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH28" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EK28" t="inlineStr"/>
+      <c r="EL28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>46081.83333333334</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>11</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>7</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Estadio Jardines del Hipódromo</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DO29" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="DZ29" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EA29" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EB29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="ED29" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE29" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EF29" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EG29" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH29" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>46081.95833333334</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Parque Luis Méndez Piana</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Avenida Ramón V. Benzano, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4350</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW30" t="inlineStr"/>
+      <c r="DX30" t="inlineStr"/>
+      <c r="DY30" t="inlineStr"/>
+      <c r="DZ30" t="inlineStr"/>
+      <c r="EA30" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EB30" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EC30" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="ED30" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EE30" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EF30" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="EG30" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EH30" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ30" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EK30" t="inlineStr"/>
+      <c r="EL30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL30" headerRowCount="1">
-  <autoFilter ref="A1:EL30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL33" headerRowCount="1">
+  <autoFilter ref="A1:EL33"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL30"/>
+  <dimension ref="A1:EL33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DE5" t="n">
         <v>1.75</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         <v>1.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4521,7 +4521,7 @@
         <v>0.5</v>
       </c>
       <c r="DE8" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DE10" t="n">
         <v>1.75</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE11" t="n">
         <v>1.75</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DE12" t="n">
         <v>0.25</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6778,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE13" t="n">
         <v>1.75</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7665,7 +7665,7 @@
         <v>2.25</v>
       </c>
       <c r="DE15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8593,7 +8593,7 @@
         <v>1.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9065,7 +9065,7 @@
         <v>0.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9513,7 +9513,7 @@
         <v>1.75</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10873,7 +10873,7 @@
         <v>0.25</v>
       </c>
       <c r="DE22" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DE24" t="n">
         <v>2.25</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12246,10 +12246,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DE25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13316,31 +13316,31 @@
         <v>5</v>
       </c>
       <c r="R28" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" t="n">
         <v>4</v>
       </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
+        <v>9</v>
+      </c>
+      <c r="V28" t="n">
         <v>8</v>
       </c>
-      <c r="V28" t="n">
-        <v>7</v>
-      </c>
       <c r="W28" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="X28" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Z28" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -13500,13 +13500,13 @@
         <v>83</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="CA28" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="CB28" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="CC28" t="n">
         <v>0</v>
@@ -13551,31 +13551,31 @@
         <v>0</v>
       </c>
       <c r="CQ28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR28" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CS28" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU28" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV28" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX28" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY28" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ28" t="n">
         <v>67</v>
@@ -14224,7 +14224,7 @@
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -14257,10 +14257,10 @@
         <v>-1</v>
       </c>
       <c r="Y30" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Z30" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>2.83</v>
@@ -14396,22 +14396,22 @@
         <v>2</v>
       </c>
       <c r="BR30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS30" t="n">
         <v>1</v>
       </c>
       <c r="BT30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BU30" t="n">
         <v>1</v>
       </c>
       <c r="BV30" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="BW30" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="BX30" t="n">
         <v>86</v>
@@ -14420,13 +14420,13 @@
         <v>97</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
       <c r="CA30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="CB30" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="CC30" t="n">
         <v>0</v>
@@ -14622,6 +14622,1406 @@
       </c>
       <c r="EK30" t="inlineStr"/>
       <c r="EL30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>46082.53125</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4357</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK31" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO31" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP31" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ31" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV31" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW31" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX31" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY31" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ31" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EA31" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EB31" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="ED31" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE31" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EF31" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EG31" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH31" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="EJ31" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EK31" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EL31" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46082.9375</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" t="n">
+        <v>8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>13</v>
+      </c>
+      <c r="W32" t="n">
+        <v>15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Estadio Gran Parque Central</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>3</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX32" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DY32" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EA32" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EB32" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="ED32" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE32" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF32" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EG32" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EH32" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EI32" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EJ32" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK32" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EL32" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>46083.95833333334</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>11</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>16</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Estadio Domingo Burgueño Miguel</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>, Maldonado</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DO33" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW33" t="inlineStr"/>
+      <c r="DX33" t="inlineStr"/>
+      <c r="DY33" t="inlineStr"/>
+      <c r="DZ33" t="inlineStr"/>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EK33" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -14684,31 +14684,31 @@
         <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W31" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="X31" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Z31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -14868,13 +14868,13 @@
         <v>67</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="CA31" t="n">
-        <v>0.8</v>
+        <v>1.38</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="CC31" t="n">
         <v>0</v>
@@ -14919,31 +14919,31 @@
         <v>0</v>
       </c>
       <c r="CQ31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR31" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="CS31" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CT31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU31" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CV31" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX31" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY31" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ31" t="n">
         <v>50</v>
@@ -15328,10 +15328,10 @@
         <v>1</v>
       </c>
       <c r="BV32" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="BW32" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="BX32" t="n">
         <v>93</v>
@@ -15340,13 +15340,13 @@
         <v>91</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
@@ -15616,7 +15616,7 @@
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -15625,50 +15625,50 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>14</v>
+      </c>
+      <c r="V33" t="n">
+        <v>10</v>
+      </c>
+      <c r="W33" t="n">
+        <v>8</v>
+      </c>
+      <c r="X33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Estadio Domingo Burgueño Miguel</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>, Maldonado</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
         <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>11</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>16</v>
-      </c>
-      <c r="V33" t="n">
-        <v>7</v>
-      </c>
-      <c r="W33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
-      <c r="AC33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3</v>
       </c>
       <c r="AE33" t="n">
         <v>1.85</v>
@@ -15788,13 +15788,13 @@
         <v>2</v>
       </c>
       <c r="BR33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS33" t="n">
         <v>2</v>
       </c>
       <c r="BT33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
@@ -15812,13 +15812,13 @@
         <v>97</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -15863,31 +15863,31 @@
         <v>0</v>
       </c>
       <c r="CQ33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
       <c r="CS33" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CT33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY33" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CZ33" t="n">
         <v>50</v>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL33" headerRowCount="1">
-  <autoFilter ref="A1:EL33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL34" headerRowCount="1">
+  <autoFilter ref="A1:EL34"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL33"/>
+  <dimension ref="A1:EL34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DE3" t="n">
         <v>1.75</v>
@@ -4065,7 +4065,7 @@
         <v>1.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         <v>0.75</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.25</v>
@@ -11326,7 +11326,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DE23" t="n">
         <v>1.75</v>
@@ -12249,7 +12249,7 @@
         <v>2.25</v>
       </c>
       <c r="DE25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -14513,7 +14513,7 @@
         <v>2.25</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE33" t="n">
         <v>0.25</v>
@@ -16022,6 +16022,446 @@
           <t>1.32</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46087.95833333334</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>13</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ34" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>63</v>
+      </c>
+      <c r="DC34" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE34" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ34" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK34" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN34" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO34" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW34" t="inlineStr"/>
+      <c r="DX34" t="inlineStr"/>
+      <c r="DY34" t="inlineStr"/>
+      <c r="DZ34" t="inlineStr"/>
+      <c r="EA34" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr"/>
+      <c r="EJ34" t="inlineStr"/>
+      <c r="EK34" t="inlineStr"/>
+      <c r="EL34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL34" headerRowCount="1">
-  <autoFilter ref="A1:EL34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL40" headerRowCount="1">
+  <autoFilter ref="A1:EL40"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL34"/>
+  <dimension ref="A1:EL40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>1.6</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE7" t="n">
         <v>2</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4521,7 +4521,7 @@
         <v>0.5</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DE10" t="n">
         <v>1.6</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5853,7 +5853,7 @@
         <v>1.75</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6325,7 +6325,7 @@
         <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6778,10 +6778,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DE14" t="n">
         <v>0.5</v>
@@ -7662,10 +7662,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8137,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8590,10 +8590,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DE18" t="n">
         <v>1.75</v>
@@ -9510,10 +9510,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10870,10 +10870,10 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11329,7 +11329,7 @@
         <v>1.6</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11782,10 +11782,10 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="DE24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE25" t="n">
         <v>2</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12678,10 +12678,10 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13134,7 +13134,7 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DE27" t="n">
         <v>0.5</v>
@@ -13593,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14038,10 +14038,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14510,7 +14510,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE30" t="n">
         <v>1.6</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14961,7 +14961,7 @@
         <v>1.75</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -15430,10 +15430,10 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15905,7 +15905,7 @@
         <v>2</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16069,46 +16069,46 @@
         <v>13</v>
       </c>
       <c r="M34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
         <v>6</v>
       </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W34" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="X34" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Z34" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
         <v>3</v>
@@ -16241,7 +16241,7 @@
         <v>2</v>
       </c>
       <c r="BQ34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
@@ -16250,16 +16250,16 @@
         <v>6</v>
       </c>
       <c r="BT34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="BW34" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="BX34" t="n">
         <v>94</v>
@@ -16268,13 +16268,13 @@
         <v>102</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.59</v>
+        <v>1.21</v>
       </c>
       <c r="CA34" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="CB34" t="n">
-        <v>1.59</v>
+        <v>2.97</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16319,31 +16319,31 @@
         <v>0</v>
       </c>
       <c r="CQ34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CS34" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CT34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CV34" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY34" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
         <v>63</v>
@@ -16462,6 +16462,2742 @@
       <c r="EJ34" t="inlineStr"/>
       <c r="EK34" t="inlineStr"/>
       <c r="EL34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46088.83333333334</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>12</v>
+      </c>
+      <c r="V35" t="n">
+        <v>10</v>
+      </c>
+      <c r="W35" t="n">
+        <v>16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Parque Abraham Paladino</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Avenida Emilio Romero, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR35" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS35" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU35" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV35" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX35" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY35" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ35" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC35" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ35" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK35" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL35" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DM35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DO35" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW35" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="DZ35" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EA35" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="ED35" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EE35" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EF35" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="EG35" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH35" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EI35" t="inlineStr"/>
+      <c r="EJ35" t="inlineStr"/>
+      <c r="EK35" t="inlineStr"/>
+      <c r="EL35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46088.97916666666</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>15</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Estadio Campeón del Siglo</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>83</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB36" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ36" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DM36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DO36" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW36" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX36" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY36" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ36" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EA36" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EB36" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC36" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="ED36" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE36" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EF36" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EG36" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH36" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI36" t="inlineStr"/>
+      <c r="EJ36" t="inlineStr"/>
+      <c r="EK36" t="inlineStr"/>
+      <c r="EL36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46089.53125</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>12</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Parque Osvaldo Roberto</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK37" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO37" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW37" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA37" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE37" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr"/>
+      <c r="EJ37" t="inlineStr"/>
+      <c r="EK37" t="inlineStr"/>
+      <c r="EL37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46089.83333333334</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Parque Artigas</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4365</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>82</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO38" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ38" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC38" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DG38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DI38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ38" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK38" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO38" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW38" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="DX38" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DY38" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="DZ38" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EA38" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>8.44</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EG38" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EH38" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI38" t="inlineStr"/>
+      <c r="EJ38" t="inlineStr"/>
+      <c r="EK38" t="inlineStr"/>
+      <c r="EL38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46089.95833333334</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>15</v>
+      </c>
+      <c r="V39" t="n">
+        <v>10</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB39" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ39" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO39" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW39" t="inlineStr"/>
+      <c r="DX39" t="inlineStr"/>
+      <c r="DY39" t="inlineStr"/>
+      <c r="DZ39" t="inlineStr"/>
+      <c r="EA39" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EB39" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EC39" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="EG39" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EH39" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr"/>
+      <c r="EJ39" t="inlineStr"/>
+      <c r="EK39" t="inlineStr"/>
+      <c r="EL39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46090.89583333334</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>6</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>104</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>137</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB40" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC40" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK40" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DM40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DO40" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP40" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW40" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX40" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY40" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DZ40" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EA40" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EG40" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH40" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EJ40" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK40" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EL40" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL40" headerRowCount="1">
-  <autoFilter ref="A1:EL40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL41" headerRowCount="1">
+  <autoFilter ref="A1:EL41"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL40"/>
+  <dimension ref="A1:EL41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DE8" t="n">
         <v>1.4</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE11" t="n">
         <v>1.6</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         <v>1.6</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -9065,7 +9065,7 @@
         <v>0.4</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10422,7 +10422,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DE21" t="n">
         <v>1</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -13137,7 +13137,7 @@
         <v>0.4</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14958,7 +14958,7 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DE31" t="n">
         <v>0.6</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -17439,28 +17439,28 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W37" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="Y37" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -17620,13 +17620,13 @@
         <v>103</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="CA37" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="CB37" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="CC37" t="n">
         <v>0</v>
@@ -17671,31 +17671,31 @@
         <v>0</v>
       </c>
       <c r="CQ37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR37" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="CS37" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CT37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU37" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CV37" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CW37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX37" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY37" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ37" t="n">
         <v>50</v>
@@ -17889,34 +17889,34 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W38" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="X38" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y38" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Z38" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -18076,13 +18076,13 @@
         <v>119</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="CA38" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="CB38" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="CC38" t="n">
         <v>0</v>
@@ -18127,31 +18127,31 @@
         <v>0</v>
       </c>
       <c r="CQ38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR38" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
       <c r="CS38" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CV38" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CW38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX38" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY38" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ38" t="n">
         <v>38</v>
@@ -18345,34 +18345,34 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S39" t="n">
+        <v>16</v>
+      </c>
+      <c r="T39" t="n">
+        <v>7</v>
+      </c>
+      <c r="U39" t="n">
+        <v>21</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" t="n">
-        <v>5</v>
-      </c>
-      <c r="U39" t="n">
-        <v>15</v>
-      </c>
-      <c r="V39" t="n">
-        <v>10</v>
-      </c>
-      <c r="W39" t="n">
-        <v>-1</v>
-      </c>
       <c r="X39" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="Y39" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Z39" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -18520,10 +18520,10 @@
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="BW39" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="BX39" t="n">
         <v>108</v>
@@ -18532,13 +18532,13 @@
         <v>102</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="CC39" t="n">
         <v>0</v>
@@ -18583,31 +18583,31 @@
         <v>0</v>
       </c>
       <c r="CQ39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR39" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="CS39" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="CT39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CV39" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX39" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY39" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ39" t="n">
         <v>38</v>
@@ -19120,17 +19120,17 @@
       </c>
       <c r="DW40" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="DX40" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -19140,64 +19140,512 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="EG40" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH40" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr"/>
+      <c r="EJ40" t="inlineStr"/>
+      <c r="EK40" t="inlineStr"/>
+      <c r="EL40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46091.02083333334</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>10</v>
+      </c>
+      <c r="V41" t="n">
+        <v>5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Parque José Nasazzi</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Avenida Leon Ribeiro, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>4357</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ41" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC41" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ41" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK41" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL41" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DM41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN41" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DO41" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP41" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW41" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DX41" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DY41" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DZ41" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA41" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB41" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EC41" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="ED41" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE41" t="inlineStr">
+        <is>
           <t>2.41</t>
         </is>
       </c>
-      <c r="EF40" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="EG40" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EH40" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EJ40" t="inlineStr">
+      <c r="EF41" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="EG41" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EH41" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI41" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EJ41" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EK40" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EL40" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
+      <c r="EK41" t="inlineStr"/>
+      <c r="EL41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL41" headerRowCount="1">
-  <autoFilter ref="A1:EL41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL42" headerRowCount="1">
+  <autoFilter ref="A1:EL42"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL41"/>
+  <dimension ref="A1:EL42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE3" t="n">
         <v>1.6</v>
@@ -4521,7 +4521,7 @@
         <v>0.4</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         <v>0.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -6778,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
         <v>2</v>
@@ -10873,7 +10873,7 @@
         <v>0.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE23" t="n">
         <v>2</v>
@@ -14513,7 +14513,7 @@
         <v>2</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15430,7 +15430,7 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE32" t="n">
         <v>2</v>
@@ -16358,7 +16358,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE34" t="n">
         <v>2</v>
@@ -18169,7 +18169,7 @@
         <v>0.8</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18785,34 +18785,34 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
         <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="X40" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="Y40" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Z40" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -18972,13 +18972,13 @@
         <v>137</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="CC40" t="n">
         <v>0</v>
@@ -19023,31 +19023,31 @@
         <v>0</v>
       </c>
       <c r="CQ40" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR40" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="CS40" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
       <c r="CT40" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CV40" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CW40" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX40" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CY40" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ40" t="n">
         <v>50</v>
@@ -19244,31 +19244,31 @@
         <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="n">
         <v>4</v>
       </c>
-      <c r="T41" t="n">
-        <v>3</v>
-      </c>
       <c r="U41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="X41" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y41" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Z41" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -19428,13 +19428,13 @@
         <v>86</v>
       </c>
       <c r="BZ41" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="CA41" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB41" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="CC41" t="n">
         <v>0</v>
@@ -19479,31 +19479,31 @@
         <v>0</v>
       </c>
       <c r="CQ41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR41" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CS41" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CT41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CV41" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX41" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY41" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ41" t="n">
         <v>38</v>
@@ -19646,6 +19646,426 @@
       </c>
       <c r="EK41" t="inlineStr"/>
       <c r="EL41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46094.95833333334</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>8</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>13</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Estadio Gran Parque Central</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>131</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ42" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC42" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ42" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK42" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO42" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP42" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ42" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW42" t="inlineStr"/>
+      <c r="DX42" t="inlineStr"/>
+      <c r="DY42" t="inlineStr"/>
+      <c r="DZ42" t="inlineStr"/>
+      <c r="EA42" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="ED42" t="inlineStr"/>
+      <c r="EE42" t="inlineStr"/>
+      <c r="EF42" t="inlineStr"/>
+      <c r="EG42" t="inlineStr"/>
+      <c r="EH42" t="inlineStr"/>
+      <c r="EI42" t="inlineStr"/>
+      <c r="EJ42" t="inlineStr"/>
+      <c r="EK42" t="inlineStr"/>
+      <c r="EL42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL42" headerRowCount="1">
-  <autoFilter ref="A1:EL42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL47" headerRowCount="1">
+  <autoFilter ref="A1:EL47"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL42"/>
+  <dimension ref="A1:EL47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE2" t="n">
         <v>2</v>
@@ -2233,7 +2233,7 @@
         <v>1.33</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE5" t="n">
         <v>2</v>
@@ -3625,7 +3625,7 @@
         <v>0.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE7" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE8" t="n">
         <v>1.67</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE9" t="n">
         <v>1.6</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DE10" t="n">
         <v>1.33</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5853,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6322,10 +6322,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6781,7 +6781,7 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         <v>1.6</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7662,10 +7662,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE15" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8134,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE18" t="n">
         <v>2</v>
@@ -9510,10 +9510,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE20" t="n">
         <v>1.6</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DE22" t="n">
         <v>1.67</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11785,7 +11785,7 @@
         <v>0.8</v>
       </c>
       <c r="DE24" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -12246,10 +12246,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE25" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12681,7 +12681,7 @@
         <v>2</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -13134,10 +13134,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13590,10 +13590,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14041,7 +14041,7 @@
         <v>1.6</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14510,7 +14510,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE30" t="n">
         <v>1.33</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14961,7 +14961,7 @@
         <v>2</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -15433,7 +15433,7 @@
         <v>1.67</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE33" t="n">
         <v>0.8</v>
@@ -16361,7 +16361,7 @@
         <v>1.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16391,7 +16391,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16798,10 +16798,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DE35" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16831,7 +16831,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17254,7 +17254,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE36" t="n">
         <v>1.6</v>
@@ -17710,10 +17710,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17743,7 +17743,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18622,10 +18622,10 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -18655,7 +18655,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19062,7 +19062,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DE40" t="n">
         <v>2</v>
@@ -19518,7 +19518,7 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE41" t="n">
         <v>2</v>
@@ -19705,34 +19705,34 @@
         <v>2</v>
       </c>
       <c r="Q42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>15</v>
+      </c>
+      <c r="V42" t="n">
         <v>8</v>
       </c>
-      <c r="R42" t="n">
-        <v>2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>13</v>
-      </c>
-      <c r="V42" t="n">
-        <v>4</v>
-      </c>
       <c r="W42" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X42" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Z42" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -19892,13 +19892,13 @@
         <v>108</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="CA42" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="CB42" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="CC42" t="n">
         <v>0</v>
@@ -19943,31 +19943,31 @@
         <v>0</v>
       </c>
       <c r="CQ42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR42" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS42" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CT42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV42" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CW42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX42" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY42" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ42" t="n">
         <v>40</v>
@@ -20067,6 +20067,2318 @@
       <c r="EK42" t="inlineStr"/>
       <c r="EL42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46095.54166666666</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>10</v>
+      </c>
+      <c r="V43" t="n">
+        <v>9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>17</v>
+      </c>
+      <c r="X43" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Luis Tróccoli</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>4378</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR43" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS43" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU43" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV43" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX43" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY43" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ43" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA43" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB43" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC43" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE43" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DJ43" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK43" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DN43" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DO43" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP43" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV43" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW43" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX43" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DY43" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DZ43" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EA43" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB43" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EC43" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="ED43" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE43" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="EG43" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH43" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EJ43" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EK43" t="inlineStr"/>
+      <c r="EL43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>46095.83333333334</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>9</v>
+      </c>
+      <c r="L44" t="n">
+        <v>13</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" t="n">
+        <v>15</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Parque José Nasazzi</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Avenida Leon Ribeiro, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ44" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA44" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB44" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC44" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD44" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE44" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG44" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI44" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ44" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK44" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DM44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DN44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO44" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP44" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW44" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DY44" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ44" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EA44" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EB44" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EC44" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="ED44" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EE44" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EF44" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="EG44" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EH44" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI44" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EJ44" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK44" t="inlineStr"/>
+      <c r="EL44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46095.97916666666</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>9</v>
+      </c>
+      <c r="U45" t="n">
+        <v>8</v>
+      </c>
+      <c r="V45" t="n">
+        <v>15</v>
+      </c>
+      <c r="W45" t="n">
+        <v>10</v>
+      </c>
+      <c r="X45" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>120</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR45" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS45" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV45" t="n">
+        <v>3</v>
+      </c>
+      <c r="CW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX45" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY45" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ45" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA45" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB45" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC45" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD45" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DE45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI45" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ45" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK45" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO45" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP45" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW45" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="DX45" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DY45" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DZ45" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EA45" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="ED45" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE45" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF45" t="inlineStr">
+        <is>
+          <t>4.54</t>
+        </is>
+      </c>
+      <c r="EG45" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EH45" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EI45" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EJ45" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EK45" t="inlineStr"/>
+      <c r="EL45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>46096.54166666666</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>6</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Parque Luis Méndez Piana</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Avenida Ramón V. Benzano, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>4371</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>98</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>88</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>147</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ46" t="n">
+        <v>30</v>
+      </c>
+      <c r="DA46" t="n">
+        <v>40</v>
+      </c>
+      <c r="DB46" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC46" t="n">
+        <v>40</v>
+      </c>
+      <c r="DD46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF46" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH46" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DJ46" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK46" t="n">
+        <v>60</v>
+      </c>
+      <c r="DL46" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN46" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DO46" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW46" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DX46" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DY46" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DZ46" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EA46" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="ED46" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EF46" t="inlineStr">
+        <is>
+          <t>5.23</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH46" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EI46" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ46" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK46" t="inlineStr"/>
+      <c r="EL46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>46096.83333333334</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>7</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>13</v>
+      </c>
+      <c r="V47" t="n">
+        <v>3</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Estadio Domingo Burgueño Miguel</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>, Maldonado</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>79</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ47" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA47" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB47" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC47" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF47" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH47" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ47" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK47" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL47" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN47" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO47" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP47" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW47" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX47" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DY47" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="DZ47" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EA47" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="ED47" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EF47" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH47" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EI47" t="inlineStr"/>
+      <c r="EJ47" t="inlineStr"/>
+      <c r="EK47" t="inlineStr"/>
+      <c r="EL47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL47" headerRowCount="1">
-  <autoFilter ref="A1:EL47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL49" headerRowCount="1">
+  <autoFilter ref="A1:EL49"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL47"/>
+  <dimension ref="A1:EL49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>0.83</v>
       </c>
       <c r="DE2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>2.17</v>
       </c>
       <c r="DE5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>0.33</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE11" t="n">
         <v>1.33</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
         <v>0.33</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8590,10 +8590,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9065,7 +9065,7 @@
         <v>0.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9969,7 +9969,7 @@
         <v>2.17</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11329,7 +11329,7 @@
         <v>1.33</v>
       </c>
       <c r="DE23" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE24" t="n">
         <v>1.67</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12678,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14038,7 +14038,7 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE29" t="n">
         <v>0.83</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14958,7 +14958,7 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DE31" t="n">
         <v>1</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15905,7 +15905,7 @@
         <v>2.17</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17257,7 +17257,7 @@
         <v>2.17</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17287,7 +17287,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18166,7 +18166,7 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE38" t="n">
         <v>1.67</v>
@@ -18199,7 +18199,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19065,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="DE40" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19521,7 +19521,7 @@
         <v>0.33</v>
       </c>
       <c r="DE41" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19551,7 +19551,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20589,34 +20589,34 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="n">
         <v>8</v>
       </c>
-      <c r="S44" t="n">
-        <v>4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>7</v>
-      </c>
       <c r="U44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
         <v>15</v>
       </c>
       <c r="W44" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X44" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z44" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -20776,13 +20776,13 @@
         <v>88</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="CA44" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="CC44" t="n">
         <v>0</v>
@@ -20827,31 +20827,31 @@
         <v>0</v>
       </c>
       <c r="CQ44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR44" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CS44" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU44" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV44" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX44" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY44" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ44" t="n">
         <v>40</v>
@@ -21523,28 +21523,28 @@
         <v>7</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W46" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X46" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -21704,13 +21704,13 @@
         <v>147</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="CB46" t="n">
-        <v>3.15</v>
+        <v>3.77</v>
       </c>
       <c r="CC46" t="n">
         <v>0</v>
@@ -21755,31 +21755,31 @@
         <v>0</v>
       </c>
       <c r="CQ46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CS46" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV46" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX46" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY46" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ46" t="n">
         <v>30</v>
@@ -21981,28 +21981,28 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U47" t="n">
+        <v>16</v>
+      </c>
+      <c r="V47" t="n">
+        <v>8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>9</v>
+      </c>
+      <c r="X47" t="n">
         <v>13</v>
-      </c>
-      <c r="V47" t="n">
-        <v>3</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>-1</v>
       </c>
       <c r="Y47" t="n">
         <v>60</v>
@@ -22168,13 +22168,13 @@
         <v>90</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="CA47" t="n">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.46</v>
+        <v>2.89</v>
       </c>
       <c r="CC47" t="n">
         <v>0</v>
@@ -22219,31 +22219,31 @@
         <v>0</v>
       </c>
       <c r="CQ47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS47" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CT47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CW47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX47" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY47" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ47" t="n">
         <v>40</v>
@@ -22378,6 +22378,918 @@
       <c r="EJ47" t="inlineStr"/>
       <c r="EK47" t="inlineStr"/>
       <c r="EL47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>46097.83333333334</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>6</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>13</v>
+      </c>
+      <c r="V48" t="n">
+        <v>8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>12</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Estadio Jardines del Hipódromo</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>4356</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY48" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ48" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA48" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB48" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC48" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK48" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN48" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO48" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW48" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DY48" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ48" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EA48" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB48" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EC48" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE48" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EF48" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr"/>
+      <c r="EJ48" t="inlineStr"/>
+      <c r="EK48" t="inlineStr"/>
+      <c r="EL48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>46097.95833333334</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>11</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" t="n">
+        <v>11</v>
+      </c>
+      <c r="U49" t="n">
+        <v>14</v>
+      </c>
+      <c r="V49" t="n">
+        <v>13</v>
+      </c>
+      <c r="W49" t="n">
+        <v>9</v>
+      </c>
+      <c r="X49" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>45</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR49" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS49" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU49" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX49" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY49" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ49" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA49" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB49" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC49" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DF49" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH49" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI49" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ49" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK49" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO49" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW49" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DX49" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DY49" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EA49" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EB49" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EC49" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="ED49" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EE49" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EF49" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EG49" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH49" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EI49" t="inlineStr"/>
+      <c r="EJ49" t="inlineStr"/>
+      <c r="EK49" t="inlineStr"/>
+      <c r="EL49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL49" headerRowCount="1">
-  <autoFilter ref="A1:EL49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL51" headerRowCount="1">
+  <autoFilter ref="A1:EL51"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL49"/>
+  <dimension ref="A1:EL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>1.33</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>2.17</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0.33</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DE10" t="n">
         <v>1.33</v>
@@ -5853,7 +5853,7 @@
         <v>1.83</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE12" t="n">
         <v>0.83</v>
@@ -6778,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE13" t="n">
         <v>2.17</v>
@@ -9510,10 +9510,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10873,7 +10873,7 @@
         <v>0.83</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -12249,7 +12249,7 @@
         <v>2.17</v>
       </c>
       <c r="DE25" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12681,7 +12681,7 @@
         <v>1.83</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -14961,7 +14961,7 @@
         <v>1.83</v>
       </c>
       <c r="DE31" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -15430,7 +15430,7 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE32" t="n">
         <v>2.17</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE33" t="n">
         <v>0.67</v>
@@ -16361,7 +16361,7 @@
         <v>1.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -18169,7 +18169,7 @@
         <v>0.67</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18622,7 +18622,7 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE39" t="n">
         <v>1.67</v>
@@ -19062,7 +19062,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DE40" t="n">
         <v>1.83</v>
@@ -19982,7 +19982,7 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE42" t="n">
         <v>1.33</v>
@@ -21797,7 +21797,7 @@
         <v>1.67</v>
       </c>
       <c r="DE46" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -22258,10 +22258,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22291,7 +22291,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23290,6 +23290,934 @@
       <c r="EJ49" t="inlineStr"/>
       <c r="EK49" t="inlineStr"/>
       <c r="EL49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>46101.875</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>14</v>
+      </c>
+      <c r="U50" t="n">
+        <v>11</v>
+      </c>
+      <c r="V50" t="n">
+        <v>18</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4371</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ50" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA50" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB50" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC50" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE50" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG50" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI50" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK50" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN50" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO50" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW50" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DX50" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DY50" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EA50" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EB50" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EC50" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EE50" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EF50" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EG50" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EH50" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EI50" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EJ50" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK50" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EL50" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46102.02083333334</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>4361</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>84</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM51" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ51" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA51" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB51" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC51" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ51" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK51" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO51" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW51" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX51" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DY51" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="DZ51" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA51" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EB51" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EF51" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EG51" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH51" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI51" t="inlineStr"/>
+      <c r="EJ51" t="inlineStr"/>
+      <c r="EK51" t="inlineStr"/>
+      <c r="EL51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL51" headerRowCount="1">
-  <autoFilter ref="A1:EL51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL57" headerRowCount="1">
+  <autoFilter ref="A1:EL57"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL51"/>
+  <dimension ref="A1:EL57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE3" t="n">
         <v>1.57</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE6" t="n">
         <v>1.29</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE7" t="n">
         <v>1.86</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE8" t="n">
         <v>1.43</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>1.29</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE11" t="n">
         <v>1.57</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6325,7 +6325,7 @@
         <v>1.86</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6781,7 +6781,7 @@
         <v>1.43</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7662,10 +7662,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8134,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8590,10 +8590,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9062,10 +9062,10 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE22" t="n">
         <v>1.43</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11326,10 +11326,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11782,10 +11782,10 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE25" t="n">
         <v>1.86</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12678,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
         <v>1.57</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13134,10 +13134,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13590,10 +13590,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14038,10 +14038,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14510,10 +14510,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14958,7 +14958,7 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE31" t="n">
         <v>1.29</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15433,7 +15433,7 @@
         <v>1.43</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15905,7 +15905,7 @@
         <v>1.86</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16358,7 +16358,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE34" t="n">
         <v>1.86</v>
@@ -16391,7 +16391,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16798,10 +16798,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16831,7 +16831,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17254,10 +17254,10 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17287,7 +17287,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17710,10 +17710,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17743,7 +17743,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18166,7 +18166,7 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE38" t="n">
         <v>1.43</v>
@@ -18199,7 +18199,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18625,7 +18625,7 @@
         <v>1.57</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -18655,7 +18655,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19065,7 +19065,7 @@
         <v>1.29</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19518,10 +19518,10 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19551,7 +19551,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19985,7 +19985,7 @@
         <v>1.43</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20015,7 +20015,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20402,10 +20402,10 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20435,7 +20435,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20866,10 +20866,10 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -20899,7 +20899,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21330,10 +21330,10 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DE45" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -21363,7 +21363,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21794,7 +21794,7 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE46" t="n">
         <v>1.29</v>
@@ -21827,7 +21827,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>70</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DF48" t="n">
         <v>1.6</v>
@@ -22747,7 +22747,7 @@
         <v>2.61</v>
       </c>
       <c r="DO48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23170,10 +23170,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23203,7 +23203,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23328,19 +23328,19 @@
         <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
         <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -23349,34 +23349,34 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
         <v>5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4</v>
       </c>
       <c r="S50" t="n">
         <v>6</v>
       </c>
       <c r="T50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W50" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X50" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="Y50" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -23389,10 +23389,10 @@
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE50" t="n">
         <v>3.47</v>
@@ -23509,16 +23509,16 @@
         <v>0</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS50" t="n">
         <v>1</v>
       </c>
       <c r="BT50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU50" t="n">
         <v>1</v>
@@ -23536,13 +23536,13 @@
         <v>98</v>
       </c>
       <c r="BZ50" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="CA50" t="n">
         <v>1.8</v>
       </c>
       <c r="CB50" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="CC50" t="n">
         <v>0</v>
@@ -23587,31 +23587,31 @@
         <v>0</v>
       </c>
       <c r="CQ50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR50" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="CS50" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU50" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CW50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX50" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY50" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ50" t="n">
         <v>42</v>
@@ -23704,47 +23704,47 @@
       </c>
       <c r="EA50" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EB50" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC50" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="ED50" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EE50" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF50" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="EG50" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EH50" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EI50" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EJ50" t="inlineStr">
@@ -24156,68 +24156,2876 @@
       </c>
       <c r="DW51" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="DX51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DY51" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ51" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA51" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB51" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF51" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EG51" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH51" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI51" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EJ51" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK51" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EL51" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46102.54166666666</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>7</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Parque Osvaldo Roberto</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ52" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA52" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB52" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC52" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD52" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DE52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF52" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG52" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DH52" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DI52" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DJ52" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK52" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN52" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO52" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP52" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW52" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="DY52" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ52" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA52" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB52" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EC52" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="ED52" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EE52" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF52" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="EG52" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EH52" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EI52" t="inlineStr"/>
+      <c r="EJ52" t="inlineStr"/>
+      <c r="EK52" t="inlineStr"/>
+      <c r="EL52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46102.66666666666</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Parque Federico Omar Saroldi</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Avenida 19 de Abril 1145 entre Atilio Pelossi y Lucas Obes, Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DO53" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW53" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DX53" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY53" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DZ53" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EA53" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EF53" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="EG53" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH53" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI53" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EJ53" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EK53" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EL53" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46102.79166666666</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="n">
+        <v>8</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>5</v>
+      </c>
+      <c r="S54" t="n">
+        <v>7</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>11</v>
+      </c>
+      <c r="V54" t="n">
+        <v>11</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>4350</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DO54" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP54" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ54" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR54" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV54" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW54" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DX54" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="DY54" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DZ54" t="inlineStr">
+        <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="DX51" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="DY51" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="DZ51" t="inlineStr">
+      <c r="EA54" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EB54" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EF54" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="EG54" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EH54" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EI54" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ54" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK54" t="inlineStr"/>
+      <c r="EL54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46102.9375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>14</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Estadio Campeón del Siglo</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT55" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU55" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW55" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DX55" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DY55" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="DZ55" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EA55" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>13.46</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46103.54166666666</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>12</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>10</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Parque Artigas</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4395</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>130</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE56" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL56" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN56" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO56" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV56" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW56" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX56" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DY56" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="DZ56" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="EA51" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="EB51" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
-      <c r="EC51" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="ED51" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EE51" t="inlineStr">
+      <c r="EA56" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="EG56" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="EF51" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EG51" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EH51" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI51" t="inlineStr"/>
-      <c r="EJ51" t="inlineStr"/>
-      <c r="EK51" t="inlineStr"/>
-      <c r="EL51" t="inlineStr"/>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr"/>
+      <c r="EJ56" t="inlineStr"/>
+      <c r="EK56" t="inlineStr"/>
+      <c r="EL56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46103.79166666666</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>11</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
+      </c>
+      <c r="V57" t="n">
+        <v>3</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Parque Abraham Paladino</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Avenida Emilio Romero, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>4363</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ57" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DE57" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI57" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL57" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM57" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DO57" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP57" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW57" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX57" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY57" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DZ57" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EA57" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB57" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EC57" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="ED57" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE57" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF57" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="EG57" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK57" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EL57" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL57" headerRowCount="1">
-  <autoFilter ref="A1:EL57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL60" headerRowCount="1">
+  <autoFilter ref="A1:EL60"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL57"/>
+  <dimension ref="A1:EL60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.29</v>
       </c>
       <c r="DE5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0.57</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>2.29</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0.71</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE10" t="n">
         <v>1.57</v>
@@ -5850,7 +5850,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
         <v>1.57</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.71</v>
@@ -6778,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE13" t="n">
         <v>2.29</v>
@@ -7662,7 +7662,7 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE15" t="n">
         <v>2.29</v>
@@ -8590,7 +8590,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE17" t="n">
         <v>0.57</v>
@@ -9065,7 +9065,7 @@
         <v>0.29</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>1.57</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -10873,7 +10873,7 @@
         <v>0.71</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>1.57</v>
       </c>
       <c r="DE23" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11785,7 +11785,7 @@
         <v>0.57</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -12249,7 +12249,7 @@
         <v>2.29</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12678,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE26" t="n">
         <v>1.57</v>
@@ -14510,7 +14510,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE30" t="n">
         <v>1.57</v>
@@ -14958,10 +14958,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15430,7 +15430,7 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE32" t="n">
         <v>2.29</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE33" t="n">
         <v>0.57</v>
@@ -16361,7 +16361,7 @@
         <v>1.57</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -18169,7 +18169,7 @@
         <v>0.57</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18625,7 +18625,7 @@
         <v>1.57</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -19062,10 +19062,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE40" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19521,7 +19521,7 @@
         <v>0.71</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19982,7 +19982,7 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE42" t="n">
         <v>1.57</v>
@@ -21794,10 +21794,10 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -21827,7 +21827,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22258,7 +22258,7 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE47" t="n">
         <v>1.57</v>
@@ -23170,10 +23170,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23203,7 +23203,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23626,10 +23626,10 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23659,7 +23659,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23827,28 +23827,28 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="n">
+        <v>8</v>
+      </c>
+      <c r="U51" t="n">
         <v>6</v>
       </c>
-      <c r="U51" t="n">
-        <v>5</v>
-      </c>
       <c r="V51" t="n">
+        <v>9</v>
+      </c>
+      <c r="W51" t="n">
         <v>7</v>
       </c>
-      <c r="W51" t="n">
-        <v>-1</v>
-      </c>
       <c r="X51" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="Y51" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Z51" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -24008,13 +24008,13 @@
         <v>121</v>
       </c>
       <c r="BZ51" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="CC51" t="n">
         <v>0</v>
@@ -24059,31 +24059,31 @@
         <v>0</v>
       </c>
       <c r="CQ51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR51" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="CS51" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU51" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CW51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX51" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY51" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ51" t="n">
         <v>25</v>
@@ -24101,7 +24101,7 @@
         <v>1.57</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24293,34 +24293,34 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W52" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="X52" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y52" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z52" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -24480,13 +24480,13 @@
         <v>101</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="CA52" t="n">
-        <v>0.78</v>
+        <v>1.23</v>
       </c>
       <c r="CB52" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="CC52" t="n">
         <v>0</v>
@@ -24531,31 +24531,31 @@
         <v>0</v>
       </c>
       <c r="CQ52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR52" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
       <c r="CS52" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
       <c r="CT52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU52" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV52" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CW52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX52" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY52" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ52" t="n">
         <v>42</v>
@@ -24573,7 +24573,7 @@
         <v>2.29</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF52" t="n">
         <v>2.17</v>
@@ -24749,34 +24749,34 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W53" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="X53" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y53" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Z53" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -24936,13 +24936,13 @@
         <v>99</v>
       </c>
       <c r="BZ53" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="CB53" t="n">
-        <v>2.11</v>
+        <v>2.81</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -24987,31 +24987,31 @@
         <v>0</v>
       </c>
       <c r="CQ53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS53" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="CT53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CV53" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CW53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX53" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY53" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ53" t="n">
         <v>50</v>
@@ -25026,10 +25026,10 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DF53" t="n">
         <v>1.83</v>
@@ -25059,7 +25059,7 @@
         <v>2.55</v>
       </c>
       <c r="DO53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25685,34 +25685,34 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U55" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W55" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="X55" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="Y55" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Z55" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -25872,13 +25872,13 @@
         <v>88</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1.66</v>
+        <v>2.44</v>
       </c>
       <c r="CA55" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="CB55" t="n">
-        <v>2.15</v>
+        <v>3.31</v>
       </c>
       <c r="CC55" t="n">
         <v>1</v>
@@ -25923,31 +25923,31 @@
         <v>0</v>
       </c>
       <c r="CQ55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CS55" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="CT55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU55" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CV55" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CW55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX55" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY55" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ55" t="n">
         <v>34</v>
@@ -27024,6 +27024,1422 @@
       <c r="EL57" t="inlineStr">
         <is>
           <t>1.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>46105.70833333334</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>9</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Estadio Domingo Burgueño Miguel</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>, Maldonado</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>62</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ58" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA58" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB58" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC58" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD58" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF58" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DI58" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ58" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK58" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL58" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO58" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP58" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV58" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW58" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX58" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DY58" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DZ58" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EA58" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EB58" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="ED58" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EE58" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF58" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EG58" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EI58" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EJ58" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EL58" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>46105.83333333334</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" t="n">
+        <v>12</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>6</v>
+      </c>
+      <c r="R59" t="n">
+        <v>3</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6</v>
+      </c>
+      <c r="T59" t="n">
+        <v>6</v>
+      </c>
+      <c r="U59" t="n">
+        <v>12</v>
+      </c>
+      <c r="V59" t="n">
+        <v>9</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ59" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK59" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL59" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM59" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ59" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA59" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB59" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC59" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE59" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DH59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DI59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DJ59" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK59" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL59" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM59" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN59" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO59" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV59" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW59" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="DX59" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DY59" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ59" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA59" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EB59" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="ED59" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EE59" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EF59" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="EG59" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EH59" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EI59" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EJ59" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46105.97916666666</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>10</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>12</v>
+      </c>
+      <c r="V60" t="n">
+        <v>6</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Estadio Gran Parque Central</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI60" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB60" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE60" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ60" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK60" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL60" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN60" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DO60" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP60" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ60" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR60" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS60" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT60" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU60" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV60" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW60" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DX60" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="DY60" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ60" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EA60" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="EB60" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC60" t="inlineStr">
+        <is>
+          <t>7.34</t>
+        </is>
+      </c>
+      <c r="ED60" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EE60" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EF60" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EG60" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH60" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EI60" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EJ60" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EK60" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EL60" t="inlineStr">
+        <is>
+          <t>1.38</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL60" headerRowCount="1">
-  <autoFilter ref="A1:EL60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL65" headerRowCount="1">
+  <autoFilter ref="A1:EL65"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL60"/>
+  <dimension ref="A1:EL65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE2" t="n">
         <v>1.5</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2230,10 +2230,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE4" t="n">
         <v>1.38</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE5" t="n">
         <v>1.75</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE6" t="n">
         <v>1.13</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE7" t="n">
         <v>2</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE8" t="n">
         <v>1.63</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>1.13</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5853,7 +5853,7 @@
         <v>1.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6325,7 +6325,7 @@
         <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6781,7 +6781,7 @@
         <v>1.63</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7665,7 +7665,7 @@
         <v>1.38</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8134,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8593,7 +8593,7 @@
         <v>1.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DE18" t="n">
         <v>1.5</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9510,7 +9510,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE19" t="n">
         <v>1.13</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE22" t="n">
         <v>1.63</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE23" t="n">
         <v>1.75</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE24" t="n">
         <v>1.38</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE25" t="n">
         <v>2</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12681,7 +12681,7 @@
         <v>1.75</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13134,10 +13134,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13590,10 +13590,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14038,10 +14038,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14513,7 +14513,7 @@
         <v>1.38</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15433,7 +15433,7 @@
         <v>1.63</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15905,7 +15905,7 @@
         <v>2</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16358,7 +16358,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE34" t="n">
         <v>2</v>
@@ -16391,7 +16391,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16798,10 +16798,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16831,7 +16831,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17254,10 +17254,10 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17287,7 +17287,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17710,10 +17710,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17743,7 +17743,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18166,7 +18166,7 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE38" t="n">
         <v>1.63</v>
@@ -18199,7 +18199,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18622,7 +18622,7 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE39" t="n">
         <v>1.38</v>
@@ -18655,7 +18655,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19518,7 +19518,7 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE41" t="n">
         <v>1.5</v>
@@ -19551,7 +19551,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19985,7 +19985,7 @@
         <v>1.63</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20015,7 +20015,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20402,10 +20402,10 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20435,7 +20435,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20866,10 +20866,10 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -20899,7 +20899,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21330,10 +21330,10 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DE45" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -21363,7 +21363,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22261,7 +22261,7 @@
         <v>2</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22291,7 +22291,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>70</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF48" t="n">
         <v>1.6</v>
@@ -22747,7 +22747,7 @@
         <v>2.61</v>
       </c>
       <c r="DO48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24098,7 +24098,7 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE51" t="n">
         <v>1.63</v>
@@ -24131,7 +24131,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24570,7 +24570,7 @@
         <v>67</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE52" t="n">
         <v>1.5</v>
@@ -24603,7 +24603,7 @@
         <v>3.02</v>
       </c>
       <c r="DO52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25498,10 +25498,10 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DF54" t="n">
         <v>1.33</v>
@@ -25531,7 +25531,7 @@
         <v>2.47</v>
       </c>
       <c r="DO54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25962,10 +25962,10 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -25995,7 +25995,7 @@
         <v>2.62</v>
       </c>
       <c r="DO55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26434,10 +26434,10 @@
         <v>83</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26467,7 +26467,7 @@
         <v>2.67</v>
       </c>
       <c r="DO56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26890,10 +26890,10 @@
         <v>58</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -26923,7 +26923,7 @@
         <v>1.94</v>
       </c>
       <c r="DO57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27085,7 +27085,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
         <v>4</v>
@@ -27094,25 +27094,25 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V58" t="n">
+        <v>12</v>
+      </c>
+      <c r="W58" t="n">
         <v>9</v>
       </c>
-      <c r="W58" t="n">
-        <v>-1</v>
-      </c>
       <c r="X58" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="Y58" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Z58" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -27272,13 +27272,13 @@
         <v>62</v>
       </c>
       <c r="BZ58" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="CA58" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="CB58" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="CC58" t="n">
         <v>0</v>
@@ -27323,31 +27323,31 @@
         <v>0</v>
       </c>
       <c r="CQ58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR58" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CS58" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV58" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX58" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CY58" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ58" t="n">
         <v>57</v>
@@ -27536,13 +27536,13 @@
         <v>6</v>
       </c>
       <c r="J59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
         <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M59" t="n">
         <v>4</v>
@@ -27557,34 +27557,34 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R59" t="n">
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U59" t="n">
+        <v>19</v>
+      </c>
+      <c r="V59" t="n">
         <v>12</v>
       </c>
-      <c r="V59" t="n">
-        <v>9</v>
-      </c>
       <c r="W59" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="X59" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="Y59" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="Z59" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -27744,13 +27744,13 @@
         <v>63</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="CA59" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.61</v>
+        <v>3.37</v>
       </c>
       <c r="CC59" t="n">
         <v>0</v>
@@ -27795,31 +27795,31 @@
         <v>0</v>
       </c>
       <c r="CQ59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR59" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS59" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CT59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV59" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX59" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY59" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ59" t="n">
         <v>43</v>
@@ -28442,6 +28442,2322 @@
           <t>1.38</t>
         </is>
       </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46106.70833333334</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>13</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>9</v>
+      </c>
+      <c r="R61" t="n">
+        <v>8</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="n">
+        <v>8</v>
+      </c>
+      <c r="U61" t="n">
+        <v>13</v>
+      </c>
+      <c r="V61" t="n">
+        <v>16</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>4395</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>91</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="CC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM61" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ61" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB61" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC61" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD61" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE61" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DI61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ61" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK61" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM61" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN61" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO61" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP61" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ61" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR61" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS61" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT61" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU61" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV61" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW61" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX61" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DY61" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DZ61" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EA61" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EB61" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EC61" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="ED61" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE61" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EF61" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="EG61" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EH61" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI61" t="inlineStr"/>
+      <c r="EJ61" t="inlineStr"/>
+      <c r="EK61" t="inlineStr"/>
+      <c r="EL61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46106.83333333334</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6</v>
+      </c>
+      <c r="L62" t="n">
+        <v>12</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>9</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>11</v>
+      </c>
+      <c r="V62" t="n">
+        <v>5</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Luis Tróccoli</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>4360</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ62" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CA62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB62" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ62" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA62" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB62" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC62" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD62" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DE62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF62" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DG62" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH62" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DI62" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DJ62" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK62" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN62" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO62" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP62" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV62" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW62" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DX62" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DY62" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DZ62" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EA62" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EB62" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EC62" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED62" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EE62" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EF62" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="EG62" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH62" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI62" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ62" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK62" t="inlineStr"/>
+      <c r="EL62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>46106.97916666666</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="n">
+        <v>16</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
+      </c>
+      <c r="V63" t="n">
+        <v>23</v>
+      </c>
+      <c r="W63" t="n">
+        <v>10</v>
+      </c>
+      <c r="X63" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Parque José Nasazzi</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Avenida Leon Ribeiro, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX63" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY63" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ63" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB63" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC63" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD63" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DE63" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DF63" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DG63" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DH63" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DI63" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DJ63" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK63" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL63" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DM63" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN63" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DO63" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP63" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ63" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR63" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS63" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT63" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU63" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV63" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW63" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DX63" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DY63" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DZ63" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EA63" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EB63" t="inlineStr">
+        <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="EC63" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED63" t="inlineStr"/>
+      <c r="EE63" t="inlineStr"/>
+      <c r="EF63" t="inlineStr"/>
+      <c r="EG63" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH63" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EJ63" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EK63" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EL63" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46107.66666666666</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>6</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>11</v>
+      </c>
+      <c r="V64" t="n">
+        <v>6</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Parque Osvaldo Roberto</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ64" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA64" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB64" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC64" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD64" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DE64" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF64" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DG64" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH64" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DI64" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ64" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK64" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL64" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN64" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO64" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP64" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ64" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR64" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS64" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT64" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU64" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV64" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW64" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DX64" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY64" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DZ64" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EA64" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EB64" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EC64" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="ED64" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EE64" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EF64" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="EG64" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH64" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ64" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK64" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EL64" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46107.79166666666</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>6</v>
+      </c>
+      <c r="V65" t="n">
+        <v>6</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Estadio Jardines del Hipódromo</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ65" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA65" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB65" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC65" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF65" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG65" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH65" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DI65" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ65" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK65" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM65" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN65" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO65" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV65" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW65" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX65" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DY65" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DZ65" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="ED65" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE65" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EF65" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="EG65" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EH65" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI65" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EJ65" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK65" t="inlineStr"/>
+      <c r="EL65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL65" headerRowCount="1">
-  <autoFilter ref="A1:EL65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL68" headerRowCount="1">
+  <autoFilter ref="A1:EL68"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL65"/>
+  <dimension ref="A1:EL68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE3" t="n">
         <v>1.5</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE7" t="n">
         <v>2</v>
@@ -4521,7 +4521,7 @@
         <v>0.63</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE9" t="n">
         <v>1.5</v>
@@ -5389,7 +5389,7 @@
         <v>1.13</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -6778,10 +6778,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7665,7 +7665,7 @@
         <v>1.38</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -8137,7 +8137,7 @@
         <v>1.38</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE17" t="n">
         <v>0.5</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE18" t="n">
         <v>1.5</v>
@@ -9966,7 +9966,7 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE20" t="n">
         <v>1.5</v>
@@ -10873,7 +10873,7 @@
         <v>0.75</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11326,10 +11326,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DE25" t="n">
         <v>2</v>
@@ -12678,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE26" t="n">
         <v>1.5</v>
@@ -13134,7 +13134,7 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE27" t="n">
         <v>0.63</v>
@@ -13593,7 +13593,7 @@
         <v>1.38</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -14513,7 +14513,7 @@
         <v>1.38</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15430,10 +15430,10 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16358,7 +16358,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE34" t="n">
         <v>2</v>
@@ -17254,7 +17254,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DE36" t="n">
         <v>1.5</v>
@@ -17710,10 +17710,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17743,7 +17743,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18169,7 +18169,7 @@
         <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -19065,7 +19065,7 @@
         <v>1.13</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19982,10 +19982,10 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20015,7 +20015,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20402,7 +20402,7 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE43" t="n">
         <v>0.75</v>
@@ -20869,7 +20869,7 @@
         <v>0.63</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -21333,7 +21333,7 @@
         <v>1.38</v>
       </c>
       <c r="DE45" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -23173,7 +23173,7 @@
         <v>1.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -24101,7 +24101,7 @@
         <v>1.5</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24570,7 +24570,7 @@
         <v>67</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE52" t="n">
         <v>1.5</v>
@@ -25026,7 +25026,7 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DE53" t="n">
         <v>1.38</v>
@@ -25498,7 +25498,7 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE54" t="n">
         <v>1.5</v>
@@ -25962,10 +25962,10 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -25995,7 +25995,7 @@
         <v>2.62</v>
       </c>
       <c r="DO55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27365,7 +27365,7 @@
         <v>2</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DF58" t="n">
         <v>1.86</v>
@@ -28035,28 +28035,28 @@
         <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T60" t="n">
         <v>4</v>
       </c>
       <c r="U60" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="V60" t="n">
         <v>6</v>
       </c>
       <c r="W60" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X60" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="Y60" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="Z60" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -28216,13 +28216,13 @@
         <v>128</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="CA60" t="n">
         <v>0.57</v>
       </c>
       <c r="CB60" t="n">
-        <v>2.24</v>
+        <v>2.67</v>
       </c>
       <c r="CC60" t="n">
         <v>0</v>
@@ -28267,31 +28267,31 @@
         <v>0</v>
       </c>
       <c r="CQ60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR60" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CS60" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CT60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU60" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CV60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CW60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX60" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY60" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ60" t="n">
         <v>43</v>
@@ -28306,7 +28306,7 @@
         <v>71</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DE60" t="n">
         <v>1.13</v>
@@ -28501,34 +28501,34 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
+        <v>8</v>
+      </c>
+      <c r="R61" t="n">
+        <v>5</v>
+      </c>
+      <c r="S61" t="n">
         <v>9</v>
       </c>
-      <c r="R61" t="n">
-        <v>8</v>
-      </c>
-      <c r="S61" t="n">
-        <v>4</v>
-      </c>
       <c r="T61" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="U61" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V61" t="n">
+        <v>22</v>
+      </c>
+      <c r="W61" t="n">
         <v>16</v>
       </c>
-      <c r="W61" t="n">
-        <v>-1</v>
-      </c>
       <c r="X61" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y61" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Z61" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -28688,13 +28688,13 @@
         <v>119</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="CA61" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="CB61" t="n">
-        <v>4.19</v>
+        <v>4.53</v>
       </c>
       <c r="CC61" t="n">
         <v>0</v>
@@ -28739,31 +28739,31 @@
         <v>0</v>
       </c>
       <c r="CQ61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR61" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS61" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CT61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU61" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV61" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CW61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX61" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY61" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ61" t="n">
         <v>50</v>
@@ -28781,7 +28781,7 @@
         <v>1.38</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF61" t="n">
         <v>1.14</v>
@@ -28957,34 +28957,34 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
+        <v>11</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="n">
         <v>9</v>
       </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4</v>
-      </c>
       <c r="U62" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W62" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X62" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="Y62" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z62" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -29144,13 +29144,13 @@
         <v>106</v>
       </c>
       <c r="BZ62" t="n">
-        <v>1.76</v>
+        <v>2.21</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="CB62" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="CC62" t="n">
         <v>0</v>
@@ -29195,31 +29195,31 @@
         <v>0</v>
       </c>
       <c r="CQ62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR62" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="CS62" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU62" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CV62" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX62" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY62" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CZ62" t="n">
         <v>43</v>
@@ -29234,7 +29234,7 @@
         <v>65</v>
       </c>
       <c r="DD62" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DE62" t="n">
         <v>0.5</v>
@@ -29701,7 +29701,7 @@
         <v>0.63</v>
       </c>
       <c r="DE63" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DF63" t="n">
         <v>0.71</v>
@@ -30158,7 +30158,7 @@
         <v>64</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -30758,6 +30758,1314 @@
       </c>
       <c r="EK65" t="inlineStr"/>
       <c r="EL65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>9</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46109.79166666666</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
+      <c r="L66" t="n">
+        <v>15</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2</v>
+      </c>
+      <c r="T66" t="n">
+        <v>8</v>
+      </c>
+      <c r="U66" t="n">
+        <v>6</v>
+      </c>
+      <c r="V66" t="n">
+        <v>10</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>4350</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ66" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA66" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB66" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC66" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD66" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DF66" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG66" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH66" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI66" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DJ66" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK66" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN66" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO66" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP66" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ66" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR66" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS66" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT66" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU66" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV66" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW66" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX66" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DY66" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DZ66" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EE66" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EF66" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="EG66" t="inlineStr"/>
+      <c r="EH66" t="inlineStr"/>
+      <c r="EI66" t="inlineStr"/>
+      <c r="EJ66" t="inlineStr"/>
+      <c r="EK66" t="inlineStr"/>
+      <c r="EL66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46109.9375</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>11</v>
+      </c>
+      <c r="V67" t="n">
+        <v>7</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>140</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO67" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU67" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW67" t="inlineStr"/>
+      <c r="DX67" t="inlineStr"/>
+      <c r="DY67" t="inlineStr"/>
+      <c r="DZ67" t="inlineStr"/>
+      <c r="EA67" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="ED67" t="inlineStr"/>
+      <c r="EE67" t="inlineStr"/>
+      <c r="EF67" t="inlineStr"/>
+      <c r="EG67" t="inlineStr"/>
+      <c r="EH67" t="inlineStr"/>
+      <c r="EI67" t="inlineStr"/>
+      <c r="EJ67" t="inlineStr"/>
+      <c r="EK67" t="inlineStr"/>
+      <c r="EL67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46110.9375</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4</v>
+      </c>
+      <c r="L68" t="n">
+        <v>8</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>7</v>
+      </c>
+      <c r="V68" t="n">
+        <v>6</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Estadio Campeón del Siglo</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>141</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI68" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK68" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL68" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN68" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DO68" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS68" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT68" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU68" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW68" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DX68" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="DY68" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ68" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EA68" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB68" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EC68" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="ED68" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE68" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EF68" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EG68" t="inlineStr"/>
+      <c r="EH68" t="inlineStr"/>
+      <c r="EI68" t="inlineStr"/>
+      <c r="EJ68" t="inlineStr"/>
+      <c r="EK68" t="inlineStr"/>
+      <c r="EL68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL68" headerRowCount="1">
-  <autoFilter ref="A1:EL68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL73" headerRowCount="1">
+  <autoFilter ref="A1:EL73"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL68"/>
+  <dimension ref="A1:EL73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>1.56</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         <v>2.22</v>
       </c>
       <c r="DE7" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE8" t="n">
         <v>1.78</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE10" t="n">
         <v>1.56</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5850,10 +5850,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6322,10 +6322,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE15" t="n">
         <v>2.11</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8134,7 +8134,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE16" t="n">
         <v>0.5600000000000001</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8593,7 +8593,7 @@
         <v>1.56</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9065,7 +9065,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9510,10 +9510,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9969,7 +9969,7 @@
         <v>2.22</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE22" t="n">
         <v>1.78</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11782,10 +11782,10 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12249,7 +12249,7 @@
         <v>2.11</v>
       </c>
       <c r="DE25" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12681,7 +12681,7 @@
         <v>1.56</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13137,7 +13137,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13590,7 +13590,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE28" t="n">
         <v>2.22</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14038,10 +14038,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14510,7 +14510,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE30" t="n">
         <v>1.56</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14958,10 +14958,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15902,10 +15902,10 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16361,7 +16361,7 @@
         <v>1.56</v>
       </c>
       <c r="DE34" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16391,7 +16391,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16798,10 +16798,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16831,7 +16831,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17257,7 +17257,7 @@
         <v>2.11</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17287,7 +17287,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18166,7 +18166,7 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE38" t="n">
         <v>1.78</v>
@@ -18199,7 +18199,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18622,10 +18622,10 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -18655,7 +18655,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19062,7 +19062,7 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE40" t="n">
         <v>1.56</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19518,10 +19518,10 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19551,7 +19551,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20405,7 +20405,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20435,7 +20435,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20866,7 +20866,7 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE44" t="n">
         <v>2.22</v>
@@ -20899,7 +20899,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21330,7 +21330,7 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE45" t="n">
         <v>2.11</v>
@@ -21363,7 +21363,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21794,10 +21794,10 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -21827,7 +21827,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22258,10 +22258,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22291,7 +22291,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>70</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF48" t="n">
         <v>1.6</v>
@@ -22747,7 +22747,7 @@
         <v>2.61</v>
       </c>
       <c r="DO48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23170,7 +23170,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE49" t="n">
         <v>1.56</v>
@@ -23203,7 +23203,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23626,10 +23626,10 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE50" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23659,7 +23659,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24098,7 +24098,7 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE51" t="n">
         <v>1.78</v>
@@ -24131,7 +24131,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24573,7 +24573,7 @@
         <v>2.22</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF52" t="n">
         <v>2.17</v>
@@ -24603,7 +24603,7 @@
         <v>3.02</v>
       </c>
       <c r="DO52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25029,7 +25029,7 @@
         <v>1.56</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF53" t="n">
         <v>1.83</v>
@@ -25059,7 +25059,7 @@
         <v>2.55</v>
       </c>
       <c r="DO53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25501,7 +25501,7 @@
         <v>1.56</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF54" t="n">
         <v>1.33</v>
@@ -25531,7 +25531,7 @@
         <v>2.47</v>
       </c>
       <c r="DO54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26434,10 +26434,10 @@
         <v>83</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26467,7 +26467,7 @@
         <v>2.67</v>
       </c>
       <c r="DO56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26890,10 +26890,10 @@
         <v>58</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -26923,7 +26923,7 @@
         <v>1.94</v>
       </c>
       <c r="DO57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27362,7 +27362,7 @@
         <v>71</v>
       </c>
       <c r="DD58" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE58" t="n">
         <v>1.56</v>
@@ -27395,7 +27395,7 @@
         <v>2.88</v>
       </c>
       <c r="DO58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27834,10 +27834,10 @@
         <v>50</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DF59" t="n">
         <v>1.57</v>
@@ -27867,7 +27867,7 @@
         <v>2.65</v>
       </c>
       <c r="DO59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28309,7 +28309,7 @@
         <v>1.78</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF60" t="n">
         <v>1.43</v>
@@ -28339,7 +28339,7 @@
         <v>2.74</v>
       </c>
       <c r="DO60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28778,7 +28778,7 @@
         <v>79</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DE61" t="n">
         <v>1.56</v>
@@ -28811,7 +28811,7 @@
         <v>2.46</v>
       </c>
       <c r="DO61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29237,7 +29237,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF62" t="n">
         <v>0.29</v>
@@ -29267,7 +29267,7 @@
         <v>2.66</v>
       </c>
       <c r="DO62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29698,7 +29698,7 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DE63" t="n">
         <v>2.11</v>
@@ -29731,7 +29731,7 @@
         <v>2.42</v>
       </c>
       <c r="DO63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30161,7 +30161,7 @@
         <v>2.22</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DF64" t="n">
         <v>2.29</v>
@@ -30191,7 +30191,7 @@
         <v>2.65</v>
       </c>
       <c r="DO64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30630,10 +30630,10 @@
         <v>64</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DF65" t="n">
         <v>1.57</v>
@@ -30663,7 +30663,7 @@
         <v>2.62</v>
       </c>
       <c r="DO65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -30817,34 +30817,34 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U66" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W66" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="X66" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="Y66" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z66" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -31004,13 +31004,13 @@
         <v>84</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="CC66" t="n">
         <v>1</v>
@@ -31055,31 +31055,31 @@
         <v>0</v>
       </c>
       <c r="CQ66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CS66" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV66" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CW66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY66" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ66" t="n">
         <v>38</v>
@@ -31172,32 +31172,32 @@
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr"/>
@@ -31265,34 +31265,34 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="n">
         <v>5</v>
       </c>
-      <c r="S67" t="n">
-        <v>5</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2</v>
-      </c>
       <c r="U67" t="n">
+        <v>17</v>
+      </c>
+      <c r="V67" t="n">
+        <v>9</v>
+      </c>
+      <c r="W67" t="n">
+        <v>14</v>
+      </c>
+      <c r="X67" t="n">
         <v>11</v>
       </c>
-      <c r="V67" t="n">
-        <v>7</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X67" t="n">
-        <v>-1</v>
-      </c>
       <c r="Y67" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Z67" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
@@ -31444,13 +31444,13 @@
         <v>78</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="CA67" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="CB67" t="n">
-        <v>2.83</v>
+        <v>3.33</v>
       </c>
       <c r="CC67" t="n">
         <v>1</v>
@@ -31495,31 +31495,31 @@
         <v>0</v>
       </c>
       <c r="CQ67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR67" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
       <c r="CS67" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CT67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV67" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CW67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY67" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ67" t="n">
         <v>50</v>
@@ -31677,34 +31677,34 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
         <v>2</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T68" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U68" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W68" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="X68" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="Y68" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Z68" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -31864,13 +31864,13 @@
         <v>96</v>
       </c>
       <c r="BZ68" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="CA68" t="n">
-        <v>0.93</v>
+        <v>1.37</v>
       </c>
       <c r="CB68" t="n">
-        <v>2.28</v>
+        <v>3.14</v>
       </c>
       <c r="CC68" t="n">
         <v>0</v>
@@ -31915,31 +31915,31 @@
         <v>0</v>
       </c>
       <c r="CQ68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR68" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS68" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CT68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU68" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV68" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CW68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX68" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY68" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ68" t="n">
         <v>44</v>
@@ -32012,37 +32012,37 @@
       </c>
       <c r="DW68" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DX68" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="DY68" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="DZ68" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EA68" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EB68" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EC68" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="ED68" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="EF68" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="EG68" t="inlineStr"/>
@@ -32066,6 +32066,2286 @@
       <c r="EJ68" t="inlineStr"/>
       <c r="EK68" t="inlineStr"/>
       <c r="EL68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46111.75</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" t="n">
+        <v>4</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>9</v>
+      </c>
+      <c r="V69" t="n">
+        <v>7</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Parque Artigas</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
+        </is>
+      </c>
+      <c r="AC69" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>4363</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS69" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT69" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU69" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW69" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX69" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DY69" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ69" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA69" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EB69" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="ED69" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE69" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EF69" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="EG69" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH69" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EI69" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EJ69" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK69" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EL69" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46111.97916666666</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>4</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>9</v>
+      </c>
+      <c r="V70" t="n">
+        <v>8</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
+        </is>
+      </c>
+      <c r="AC70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>4371</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL70" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN70" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP70" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ70" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW70" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DX70" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DY70" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="ED70" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE70" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EF70" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="EG70" t="inlineStr"/>
+      <c r="EH70" t="inlineStr"/>
+      <c r="EI70" t="inlineStr"/>
+      <c r="EJ70" t="inlineStr"/>
+      <c r="EK70" t="inlineStr"/>
+      <c r="EL70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>12</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="n">
+        <v>6</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>7</v>
+      </c>
+      <c r="R71" t="n">
+        <v>4</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>8</v>
+      </c>
+      <c r="V71" t="n">
+        <v>9</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Parque Luis Méndez Piana</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Avenida Ramón V. Benzano, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>4377</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>73</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>68</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN71" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB71" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC71" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD71" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE71" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG71" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI71" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK71" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM71" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN71" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO71" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW71" t="inlineStr"/>
+      <c r="DX71" t="inlineStr"/>
+      <c r="DY71" t="inlineStr"/>
+      <c r="DZ71" t="inlineStr"/>
+      <c r="EA71" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EB71" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EC71" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="ED71" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE71" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EF71" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EG71" t="inlineStr"/>
+      <c r="EH71" t="inlineStr"/>
+      <c r="EI71" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ71" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EK71" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EL71" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46112.58333333334</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J72" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" t="n">
+        <v>6</v>
+      </c>
+      <c r="L72" t="n">
+        <v>12</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" t="n">
+        <v>4</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="n">
+        <v>7</v>
+      </c>
+      <c r="U72" t="n">
+        <v>12</v>
+      </c>
+      <c r="V72" t="n">
+        <v>11</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Parque Abraham Paladino</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Avenida Emilio Romero, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>94</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC72" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD72" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE72" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF72" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH72" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK72" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL72" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DM72" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN72" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DO72" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW72" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DX72" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DY72" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ72" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EA72" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EB72" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="EC72" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="ED72" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE72" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF72" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="EG72" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH72" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EJ72" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EK72" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EL72" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46112.91666666666</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>6</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10</v>
+      </c>
+      <c r="M73" t="n">
+        <v>4</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6</v>
+      </c>
+      <c r="S73" t="n">
+        <v>6</v>
+      </c>
+      <c r="T73" t="n">
+        <v>11</v>
+      </c>
+      <c r="U73" t="n">
+        <v>8</v>
+      </c>
+      <c r="V73" t="n">
+        <v>17</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ73" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB73" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ73" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA73" t="n">
+        <v>51</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC73" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD73" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE73" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG73" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI73" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ73" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK73" t="n">
+        <v>51</v>
+      </c>
+      <c r="DL73" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN73" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO73" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW73" t="inlineStr"/>
+      <c r="DX73" t="inlineStr"/>
+      <c r="DY73" t="inlineStr"/>
+      <c r="DZ73" t="inlineStr"/>
+      <c r="EA73" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EB73" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EC73" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="ED73" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EE73" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EF73" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="EG73" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EH73" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EI73" t="inlineStr"/>
+      <c r="EJ73" t="inlineStr"/>
+      <c r="EK73" t="inlineStr"/>
+      <c r="EL73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -31701,10 +31701,10 @@
         <v>16</v>
       </c>
       <c r="Y68" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z68" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -32131,22 +32131,22 @@
         <v>5</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U69" t="n">
+        <v>13</v>
+      </c>
+      <c r="V69" t="n">
+        <v>12</v>
+      </c>
+      <c r="W69" t="n">
+        <v>19</v>
+      </c>
+      <c r="X69" t="n">
         <v>9</v>
-      </c>
-      <c r="V69" t="n">
-        <v>7</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X69" t="n">
-        <v>-1</v>
       </c>
       <c r="Y69" t="n">
         <v>52</v>
@@ -32312,13 +32312,13 @@
         <v>92</v>
       </c>
       <c r="BZ69" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="CC69" t="n">
         <v>0</v>
@@ -32363,31 +32363,31 @@
         <v>0</v>
       </c>
       <c r="CQ69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR69" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CS69" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CT69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU69" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV69" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CW69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX69" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY69" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ69" t="n">
         <v>32</v>
@@ -32597,28 +32597,28 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U70" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V70" t="n">
         <v>8</v>
       </c>
       <c r="W70" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="X70" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y70" t="n">
         <v>48</v>
@@ -32784,13 +32784,13 @@
         <v>105</v>
       </c>
       <c r="BZ70" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CC70" t="n">
         <v>0</v>
@@ -32835,31 +32835,31 @@
         <v>0</v>
       </c>
       <c r="CQ70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR70" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CS70" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
       <c r="CT70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV70" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CW70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX70" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY70" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ70" t="n">
         <v>50</v>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL73" headerRowCount="1">
-  <autoFilter ref="A1:EL73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL79" headerRowCount="1">
+  <autoFilter ref="A1:EL79"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL73"/>
+  <dimension ref="A1:EL79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE2" t="n">
         <v>1.44</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE3" t="n">
         <v>1.44</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE7" t="n">
         <v>1.78</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5386,10 +5386,10 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5419,7 +5419,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6325,7 +6325,7 @@
         <v>1.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6778,10 +6778,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6811,7 +6811,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7198,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7231,7 +7231,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7662,10 +7662,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7695,7 +7695,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8134,7 +8134,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE16" t="n">
         <v>0.5600000000000001</v>
@@ -8590,10 +8590,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9513,7 +9513,7 @@
         <v>1.44</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9966,10 +9966,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9999,7 +9999,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10870,10 +10870,10 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11326,10 +11326,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11359,7 +11359,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11782,10 +11782,10 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -11815,7 +11815,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE25" t="n">
         <v>1.78</v>
@@ -12678,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE26" t="n">
         <v>1.44</v>
@@ -13137,7 +13137,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13590,10 +13590,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13623,7 +13623,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14038,10 +14038,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14071,7 +14071,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14510,10 +14510,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14543,7 +14543,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14961,7 +14961,7 @@
         <v>1.44</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -15430,10 +15430,10 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15463,7 +15463,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15905,7 +15905,7 @@
         <v>1.78</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -16358,7 +16358,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE34" t="n">
         <v>1.78</v>
@@ -16798,10 +16798,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16831,7 +16831,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17254,10 +17254,10 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17287,7 +17287,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17710,7 +17710,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE37" t="n">
         <v>0.5600000000000001</v>
@@ -18166,10 +18166,10 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18199,7 +18199,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18625,7 +18625,7 @@
         <v>1.44</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -19062,10 +19062,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19518,7 +19518,7 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE41" t="n">
         <v>1.44</v>
@@ -19982,10 +19982,10 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20015,7 +20015,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20405,7 +20405,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20866,10 +20866,10 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -20899,7 +20899,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21330,10 +21330,10 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE45" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -21363,7 +21363,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21794,10 +21794,10 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -21827,7 +21827,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22714,10 +22714,10 @@
         <v>70</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF48" t="n">
         <v>1.6</v>
@@ -22747,7 +22747,7 @@
         <v>2.61</v>
       </c>
       <c r="DO48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23173,7 +23173,7 @@
         <v>1.44</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23626,7 +23626,7 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE50" t="n">
         <v>1.78</v>
@@ -24101,7 +24101,7 @@
         <v>1.44</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24570,7 +24570,7 @@
         <v>67</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE52" t="n">
         <v>1.44</v>
@@ -25026,10 +25026,10 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF53" t="n">
         <v>1.83</v>
@@ -25059,7 +25059,7 @@
         <v>2.55</v>
       </c>
       <c r="DO53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25498,10 +25498,10 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF54" t="n">
         <v>1.33</v>
@@ -25531,7 +25531,7 @@
         <v>2.47</v>
       </c>
       <c r="DO54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25962,7 +25962,7 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE55" t="n">
         <v>0.5600000000000001</v>
@@ -26434,10 +26434,10 @@
         <v>83</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26467,7 +26467,7 @@
         <v>2.67</v>
       </c>
       <c r="DO56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26890,10 +26890,10 @@
         <v>58</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -26923,7 +26923,7 @@
         <v>1.94</v>
       </c>
       <c r="DO57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27365,7 +27365,7 @@
         <v>1.78</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DF58" t="n">
         <v>1.86</v>
@@ -27837,7 +27837,7 @@
         <v>1.44</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DF59" t="n">
         <v>1.57</v>
@@ -28306,10 +28306,10 @@
         <v>71</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF60" t="n">
         <v>1.43</v>
@@ -28339,7 +28339,7 @@
         <v>2.74</v>
       </c>
       <c r="DO60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28778,10 +28778,10 @@
         <v>79</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF61" t="n">
         <v>1.14</v>
@@ -28811,7 +28811,7 @@
         <v>2.46</v>
       </c>
       <c r="DO61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29237,7 +29237,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF62" t="n">
         <v>0.29</v>
@@ -29698,10 +29698,10 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE63" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DF63" t="n">
         <v>0.71</v>
@@ -29731,7 +29731,7 @@
         <v>2.42</v>
       </c>
       <c r="DO63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30158,10 +30158,10 @@
         <v>64</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DF64" t="n">
         <v>2.29</v>
@@ -30191,7 +30191,7 @@
         <v>2.65</v>
       </c>
       <c r="DO64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30630,7 +30630,7 @@
         <v>64</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE65" t="n">
         <v>1.44</v>
@@ -31094,7 +31094,7 @@
         <v>57</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE66" t="n">
         <v>0.5600000000000001</v>
@@ -31534,10 +31534,10 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF67" t="n">
         <v>1.75</v>
@@ -31567,7 +31567,7 @@
         <v>2.77</v>
       </c>
       <c r="DO67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31954,10 +31954,10 @@
         <v>69</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF68" t="n">
         <v>2.38</v>
@@ -31987,7 +31987,7 @@
         <v>3.21</v>
       </c>
       <c r="DO68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32402,10 +32402,10 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -32435,7 +32435,7 @@
         <v>2.31</v>
       </c>
       <c r="DO69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32874,10 +32874,10 @@
         <v>69</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF70" t="n">
         <v>1.13</v>
@@ -32907,7 +32907,7 @@
         <v>2.45</v>
       </c>
       <c r="DO70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33322,7 +33322,7 @@
         <v>63</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DE71" t="n">
         <v>1.78</v>
@@ -33770,7 +33770,7 @@
         <v>69</v>
       </c>
       <c r="DD72" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE72" t="n">
         <v>1.44</v>
@@ -34245,7 +34245,7 @@
         <v>1.44</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DF73" t="n">
         <v>1.5</v>
@@ -34346,6 +34346,2742 @@
       <c r="EJ73" t="inlineStr"/>
       <c r="EK73" t="inlineStr"/>
       <c r="EL73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>10</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>10</v>
+      </c>
+      <c r="R74" t="n">
+        <v>5</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="n">
+        <v>10</v>
+      </c>
+      <c r="U74" t="n">
+        <v>15</v>
+      </c>
+      <c r="V74" t="n">
+        <v>15</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Parque José Nasazzi</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Avenida Leon Ribeiro, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>4363</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>70</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>56</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF74" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI74" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK74" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL74" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DM74" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN74" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DO74" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW74" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX74" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EA74" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="ED74" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE74" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF74" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="EG74" t="inlineStr"/>
+      <c r="EH74" t="inlineStr"/>
+      <c r="EI74" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EJ74" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK74" t="inlineStr"/>
+      <c r="EL74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>46115.97916666666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>10</v>
+      </c>
+      <c r="V75" t="n">
+        <v>4</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Estadio Gran Parque Central</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>4377</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>105</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>140</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK75" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM75" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN75" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO75" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW75" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX75" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EA75" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+      <c r="ED75" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF75" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EG75" t="inlineStr"/>
+      <c r="EH75" t="inlineStr"/>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EJ75" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>46116.54166666666</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" t="n">
+        <v>5</v>
+      </c>
+      <c r="U76" t="n">
+        <v>8</v>
+      </c>
+      <c r="V76" t="n">
+        <v>7</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Parque Osvaldo Roberto</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>4354</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM76" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN76" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DO76" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW76" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DX76" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="ED76" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EG76" t="inlineStr"/>
+      <c r="EH76" t="inlineStr"/>
+      <c r="EI76" t="inlineStr"/>
+      <c r="EJ76" t="inlineStr"/>
+      <c r="EK76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46116.77083333334</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" t="n">
+        <v>11</v>
+      </c>
+      <c r="M77" t="n">
+        <v>4</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="n">
+        <v>13</v>
+      </c>
+      <c r="U77" t="n">
+        <v>9</v>
+      </c>
+      <c r="V77" t="n">
+        <v>15</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Estadio Jardines del Hipódromo</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>81</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW77" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DX77" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="ED77" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr"/>
+      <c r="EH77" t="inlineStr"/>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr"/>
+      <c r="EL77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46116.91666666666</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>8</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>7</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
+      </c>
+      <c r="V78" t="n">
+        <v>15</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>88</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW78" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX78" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>7.42</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr"/>
+      <c r="EH78" t="inlineStr"/>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46117.54166666666</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" t="n">
+        <v>10</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>6</v>
+      </c>
+      <c r="V79" t="n">
+        <v>8</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW79" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DX79" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr"/>
+      <c r="EH79" t="inlineStr"/>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr"/>
+      <c r="EL79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL79" headerRowCount="1">
-  <autoFilter ref="A1:EL79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL81" headerRowCount="1">
+  <autoFilter ref="A1:EL81"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL79"/>
+  <dimension ref="A1:EL81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.3</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>1.4</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         <v>2.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DE9" t="n">
         <v>1.3</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5850,10 +5850,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5883,7 +5883,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE12" t="n">
         <v>0.7</v>
@@ -6355,7 +6355,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8137,7 +8137,7 @@
         <v>1.3</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9062,10 +9062,10 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9510,7 +9510,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE19" t="n">
         <v>1.3</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -12249,7 +12249,7 @@
         <v>2.2</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12279,7 +12279,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12681,7 +12681,7 @@
         <v>1.5</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13134,7 +13134,7 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DE27" t="n">
         <v>1.1</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14958,7 +14958,7 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE31" t="n">
         <v>1.3</v>
@@ -14991,7 +14991,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE33" t="n">
         <v>0.4</v>
@@ -15935,7 +15935,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16361,7 +16361,7 @@
         <v>1.4</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16391,7 +16391,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -17713,7 +17713,7 @@
         <v>2.3</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17743,7 +17743,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18622,7 +18622,7 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE39" t="n">
         <v>1.7</v>
@@ -18655,7 +18655,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19521,7 +19521,7 @@
         <v>1.1</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19551,7 +19551,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20402,7 +20402,7 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DE43" t="n">
         <v>0.7</v>
@@ -20435,7 +20435,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22258,10 +22258,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22291,7 +22291,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23170,7 +23170,7 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE49" t="n">
         <v>1.5</v>
@@ -23203,7 +23203,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23629,7 +23629,7 @@
         <v>1.3</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23659,7 +23659,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24098,7 +24098,7 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE51" t="n">
         <v>1.6</v>
@@ -24131,7 +24131,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24573,7 +24573,7 @@
         <v>2.3</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF52" t="n">
         <v>2.17</v>
@@ -24603,7 +24603,7 @@
         <v>3.02</v>
       </c>
       <c r="DO52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25965,7 +25965,7 @@
         <v>2.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -25995,7 +25995,7 @@
         <v>2.62</v>
       </c>
       <c r="DO55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27362,7 +27362,7 @@
         <v>71</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DE58" t="n">
         <v>1.5</v>
@@ -27395,7 +27395,7 @@
         <v>2.88</v>
       </c>
       <c r="DO58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27834,7 +27834,7 @@
         <v>50</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE59" t="n">
         <v>1.7</v>
@@ -27867,7 +27867,7 @@
         <v>2.65</v>
       </c>
       <c r="DO59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29234,7 +29234,7 @@
         <v>65</v>
       </c>
       <c r="DD62" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DE62" t="n">
         <v>0.4</v>
@@ -29267,7 +29267,7 @@
         <v>2.66</v>
       </c>
       <c r="DO62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30633,7 +30633,7 @@
         <v>1.3</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF65" t="n">
         <v>1.57</v>
@@ -30663,7 +30663,7 @@
         <v>2.62</v>
       </c>
       <c r="DO65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -31097,7 +31097,7 @@
         <v>1.4</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="DF66" t="n">
         <v>1.38</v>
@@ -31127,7 +31127,7 @@
         <v>2.78</v>
       </c>
       <c r="DO66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>1.7</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF71" t="n">
         <v>1.38</v>
@@ -33355,7 +33355,7 @@
         <v>2.87</v>
       </c>
       <c r="DO71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33773,7 +33773,7 @@
         <v>0.7</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF72" t="n">
         <v>0.75</v>
@@ -33803,7 +33803,7 @@
         <v>2.38</v>
       </c>
       <c r="DO72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34242,7 +34242,7 @@
         <v>69</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE73" t="n">
         <v>1.3</v>
@@ -34275,7 +34275,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34861,34 +34861,34 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R75" t="n">
         <v>2</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="V75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W75" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="X75" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="Y75" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Z75" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -35048,13 +35048,13 @@
         <v>83</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.61</v>
+        <v>2.63</v>
       </c>
       <c r="CA75" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
@@ -35099,31 +35099,31 @@
         <v>0</v>
       </c>
       <c r="CQ75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CS75" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CT75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU75" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CV75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CW75" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX75" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY75" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CZ75" t="n">
         <v>62</v>
@@ -36229,28 +36229,28 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
+        <v>7</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
         <v>8</v>
       </c>
-      <c r="S78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>7</v>
-      </c>
       <c r="U78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V78" t="n">
         <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="X78" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y78" t="n">
         <v>40</v>
@@ -36408,13 +36408,13 @@
         <v>127</v>
       </c>
       <c r="BZ78" t="n">
-        <v>0.54</v>
+        <v>0.92</v>
       </c>
       <c r="CA78" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="CB78" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="CC78" t="n">
         <v>0</v>
@@ -36459,31 +36459,31 @@
         <v>0</v>
       </c>
       <c r="CQ78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS78" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CT78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU78" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CW78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CY78" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ78" t="n">
         <v>50</v>
@@ -37082,6 +37082,910 @@
       </c>
       <c r="EK79" t="inlineStr"/>
       <c r="EL79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46117.77083333334</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>11</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>5</v>
+      </c>
+      <c r="V80" t="n">
+        <v>6</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Luis Tróccoli</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>4360</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>28</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW80" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DX80" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr"/>
+      <c r="EH80" t="inlineStr"/>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr"/>
+      <c r="EL80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46117.89583333334</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>7</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>10</v>
+      </c>
+      <c r="V81" t="n">
+        <v>5</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW81" t="inlineStr"/>
+      <c r="DX81" t="inlineStr"/>
+      <c r="DY81" t="inlineStr"/>
+      <c r="DZ81" t="inlineStr"/>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="ED81" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr"/>
+      <c r="EH81" t="inlineStr"/>
+      <c r="EI81" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -36688,31 +36688,31 @@
         <v>3</v>
       </c>
       <c r="R79" t="n">
+        <v>8</v>
+      </c>
+      <c r="S79" t="n">
         <v>6</v>
       </c>
-      <c r="S79" t="n">
-        <v>3</v>
-      </c>
       <c r="T79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U79" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V79" t="n">
+        <v>18</v>
+      </c>
+      <c r="W79" t="n">
         <v>8</v>
       </c>
-      <c r="W79" t="n">
-        <v>-1</v>
-      </c>
       <c r="X79" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="Y79" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Z79" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -36872,13 +36872,13 @@
         <v>118</v>
       </c>
       <c r="BZ79" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.26</v>
+        <v>3.21</v>
       </c>
       <c r="CC79" t="n">
         <v>2</v>
@@ -36923,31 +36923,31 @@
         <v>1</v>
       </c>
       <c r="CQ79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="CS79" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CT79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV79" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CW79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY79" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CZ79" t="n">
         <v>50</v>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL81" headerRowCount="1">
-  <autoFilter ref="A1:EL81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL85" headerRowCount="1">
+  <autoFilter ref="A1:EL85"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL81"/>
+  <dimension ref="A1:EL85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE2" t="n">
         <v>1.3</v>
@@ -2233,7 +2233,7 @@
         <v>1.4</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0.4</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>2.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4518,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE9" t="n">
         <v>1.3</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DE10" t="n">
         <v>1.4</v>
@@ -5853,7 +5853,7 @@
         <v>1.3</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6322,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE12" t="n">
         <v>0.7</v>
@@ -6778,7 +6778,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE13" t="n">
         <v>2.3</v>
@@ -7201,7 +7201,7 @@
         <v>1.3</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -8134,10 +8134,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8590,7 +8590,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE17" t="n">
         <v>0.4</v>
@@ -9062,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE18" t="n">
         <v>1.3</v>
@@ -9510,10 +9510,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9543,7 +9543,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10422,10 +10422,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10873,7 +10873,7 @@
         <v>0.7</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>1.4</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -12249,7 +12249,7 @@
         <v>2.2</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12678,10 +12678,10 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12711,7 +12711,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13134,10 +13134,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13167,7 +13167,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13590,7 +13590,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE28" t="n">
         <v>2.3</v>
@@ -14961,7 +14961,7 @@
         <v>1.3</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -15430,7 +15430,7 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE32" t="n">
         <v>2.2</v>
@@ -15902,7 +15902,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE33" t="n">
         <v>0.4</v>
@@ -16361,7 +16361,7 @@
         <v>1.4</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16801,7 +16801,7 @@
         <v>0.7</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -17713,7 +17713,7 @@
         <v>2.3</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -18169,7 +18169,7 @@
         <v>0.4</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18622,7 +18622,7 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE39" t="n">
         <v>1.7</v>
@@ -19062,10 +19062,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19095,7 +19095,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19518,7 +19518,7 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE41" t="n">
         <v>1.3</v>
@@ -19982,7 +19982,7 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE42" t="n">
         <v>1.4</v>
@@ -20402,7 +20402,7 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE43" t="n">
         <v>0.7</v>
@@ -20866,7 +20866,7 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE44" t="n">
         <v>2.3</v>
@@ -21330,7 +21330,7 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE45" t="n">
         <v>2.2</v>
@@ -21797,7 +21797,7 @@
         <v>1.7</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -22258,10 +22258,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22291,7 +22291,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23173,7 +23173,7 @@
         <v>1.3</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23626,10 +23626,10 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23659,7 +23659,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24098,10 +24098,10 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24131,7 +24131,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25026,7 +25026,7 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE53" t="n">
         <v>1.7</v>
@@ -25965,7 +25965,7 @@
         <v>2.2</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -26437,7 +26437,7 @@
         <v>0.4</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26893,7 +26893,7 @@
         <v>0.7</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -27362,10 +27362,10 @@
         <v>71</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF58" t="n">
         <v>1.86</v>
@@ -27395,7 +27395,7 @@
         <v>2.88</v>
       </c>
       <c r="DO58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28306,10 +28306,10 @@
         <v>71</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF60" t="n">
         <v>1.43</v>
@@ -28339,7 +28339,7 @@
         <v>2.74</v>
       </c>
       <c r="DO60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28778,7 +28778,7 @@
         <v>79</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE61" t="n">
         <v>1.4</v>
@@ -29234,7 +29234,7 @@
         <v>65</v>
       </c>
       <c r="DD62" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE62" t="n">
         <v>0.4</v>
@@ -29698,7 +29698,7 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE63" t="n">
         <v>2.2</v>
@@ -30633,7 +30633,7 @@
         <v>1.3</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF65" t="n">
         <v>1.57</v>
@@ -31097,7 +31097,7 @@
         <v>1.4</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DF66" t="n">
         <v>1.38</v>
@@ -31534,10 +31534,10 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DF67" t="n">
         <v>1.75</v>
@@ -31567,7 +31567,7 @@
         <v>2.77</v>
       </c>
       <c r="DO67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32405,7 +32405,7 @@
         <v>0.4</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -32874,7 +32874,7 @@
         <v>69</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DE70" t="n">
         <v>1.3</v>
@@ -33325,7 +33325,7 @@
         <v>1.7</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF71" t="n">
         <v>1.38</v>
@@ -34242,10 +34242,10 @@
         <v>69</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF73" t="n">
         <v>1.5</v>
@@ -34275,7 +34275,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34682,7 +34682,7 @@
         <v>56</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE74" t="n">
         <v>1.4</v>
@@ -35138,7 +35138,7 @@
         <v>67</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE75" t="n">
         <v>1.7</v>
@@ -36053,7 +36053,7 @@
         <v>1.3</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DF77" t="n">
         <v>1.33</v>
@@ -36962,10 +36962,10 @@
         <v>84</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DF79" t="n">
         <v>1.33</v>
@@ -36995,7 +36995,7 @@
         <v>2.58</v>
       </c>
       <c r="DO79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37418,10 +37418,10 @@
         <v>50</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DF80" t="n">
         <v>0.5600000000000001</v>
@@ -37451,7 +37451,7 @@
         <v>2.62</v>
       </c>
       <c r="DO80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37877,7 +37877,7 @@
         <v>1.3</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DF81" t="n">
         <v>1.44</v>
@@ -37984,6 +37984,1830 @@
       <c r="EL81" t="inlineStr">
         <is>
           <t>1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46122.95833333334</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3</v>
+      </c>
+      <c r="R82" t="n">
+        <v>4</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>13</v>
+      </c>
+      <c r="U82" t="n">
+        <v>10</v>
+      </c>
+      <c r="V82" t="n">
+        <v>17</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW82" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DX82" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr"/>
+      <c r="EH82" t="inlineStr"/>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr"/>
+      <c r="EL82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46123.54166666666</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>8</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>13</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="n">
+        <v>4</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>4</v>
+      </c>
+      <c r="V83" t="n">
+        <v>4</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>4395</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE83" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DF83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK83" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL83" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM83" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN83" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO83" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW83" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX83" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr"/>
+      <c r="EH83" t="inlineStr"/>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>11</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46123.77083333334</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>5</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>6</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>11</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>4361</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>45</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW84" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DX84" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="EG84" t="inlineStr"/>
+      <c r="EH84" t="inlineStr"/>
+      <c r="EI84" t="inlineStr"/>
+      <c r="EJ84" t="inlineStr"/>
+      <c r="EK84" t="inlineStr"/>
+      <c r="EL84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46123.91666666666</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>6</v>
+      </c>
+      <c r="R85" t="n">
+        <v>5</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="n">
+        <v>6</v>
+      </c>
+      <c r="U85" t="n">
+        <v>10</v>
+      </c>
+      <c r="V85" t="n">
+        <v>11</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Estadio Domingo Burgueño Miguel</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>, Maldonado</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO85" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW85" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX85" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr"/>
+      <c r="EH85" t="inlineStr"/>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.34</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL129" headerRowCount="1">
-  <autoFilter ref="A1:EL129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL136" headerRowCount="1">
+  <autoFilter ref="A1:EL136"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL129"/>
+  <dimension ref="A1:EL136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2674,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3613,7 +3613,7 @@
         <v>1.13</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE7" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4926,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE9" t="n">
         <v>1.13</v>
@@ -5374,10 +5374,10 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5407,7 +5407,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5838,10 +5838,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5871,7 +5871,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6310,10 +6310,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6343,7 +6343,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6766,10 +6766,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6799,7 +6799,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7189,7 +7189,7 @@
         <v>1.13</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7650,10 +7650,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7683,7 +7683,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8122,10 +8122,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8578,7 +8578,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE17" t="n">
         <v>1.13</v>
@@ -9050,10 +9050,10 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9498,10 +9498,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9531,7 +9531,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE20" t="n">
         <v>1.13</v>
@@ -10410,10 +10410,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10858,10 +10858,10 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10891,7 +10891,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11314,10 +11314,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11347,7 +11347,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11773,7 +11773,7 @@
         <v>1.13</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -12234,10 +12234,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE25" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12267,7 +12267,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12666,10 +12666,10 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12699,7 +12699,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13122,10 +13122,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13155,7 +13155,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13578,10 +13578,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13611,7 +13611,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14029,7 +14029,7 @@
         <v>1.13</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14498,10 +14498,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14531,7 +14531,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14946,10 +14946,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -14979,7 +14979,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15418,10 +15418,10 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15451,7 +15451,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15890,7 +15890,7 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE33" t="n">
         <v>1.13</v>
@@ -16346,10 +16346,10 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE34" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16379,7 +16379,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16786,10 +16786,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16819,7 +16819,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17242,7 +17242,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE36" t="n">
         <v>1.13</v>
@@ -17698,10 +17698,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17731,7 +17731,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18157,7 +18157,7 @@
         <v>1.13</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18610,10 +18610,10 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -18643,7 +18643,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19050,10 +19050,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19083,7 +19083,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19506,10 +19506,10 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19539,7 +19539,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19970,10 +19970,10 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20003,7 +20003,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20390,10 +20390,10 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20423,7 +20423,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20854,10 +20854,10 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -20887,7 +20887,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21318,10 +21318,10 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -21351,7 +21351,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21782,10 +21782,10 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -21815,7 +21815,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22246,10 +22246,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22279,7 +22279,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23158,10 +23158,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23191,7 +23191,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23614,10 +23614,10 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE50" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23647,7 +23647,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24086,10 +24086,10 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24119,7 +24119,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24558,10 +24558,10 @@
         <v>67</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF52" t="n">
         <v>2.17</v>
@@ -24591,7 +24591,7 @@
         <v>3.02</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25014,10 +25014,10 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF53" t="n">
         <v>1.83</v>
@@ -25047,7 +25047,7 @@
         <v>2.55</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25486,7 +25486,7 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE54" t="n">
         <v>1.13</v>
@@ -25950,10 +25950,10 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -25983,7 +25983,7 @@
         <v>2.62</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26425,7 +26425,7 @@
         <v>1.13</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26878,10 +26878,10 @@
         <v>58</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -26911,7 +26911,7 @@
         <v>1.94</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27350,10 +27350,10 @@
         <v>71</v>
       </c>
       <c r="DD58" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF58" t="n">
         <v>1.86</v>
@@ -27383,7 +27383,7 @@
         <v>2.88</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27822,10 +27822,10 @@
         <v>50</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF59" t="n">
         <v>1.57</v>
@@ -27855,7 +27855,7 @@
         <v>2.65</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28294,10 +28294,10 @@
         <v>71</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF60" t="n">
         <v>1.43</v>
@@ -28327,7 +28327,7 @@
         <v>2.74</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28766,10 +28766,10 @@
         <v>79</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF61" t="n">
         <v>1.14</v>
@@ -28799,7 +28799,7 @@
         <v>2.46</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29222,7 +29222,7 @@
         <v>65</v>
       </c>
       <c r="DD62" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE62" t="n">
         <v>1.13</v>
@@ -29686,10 +29686,10 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF63" t="n">
         <v>0.71</v>
@@ -29719,7 +29719,7 @@
         <v>2.42</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30146,10 +30146,10 @@
         <v>64</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF64" t="n">
         <v>2.29</v>
@@ -30179,7 +30179,7 @@
         <v>2.65</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30621,7 +30621,7 @@
         <v>1.13</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF65" t="n">
         <v>1.57</v>
@@ -31082,10 +31082,10 @@
         <v>57</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF66" t="n">
         <v>1.38</v>
@@ -31115,7 +31115,7 @@
         <v>2.78</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31522,10 +31522,10 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF67" t="n">
         <v>1.75</v>
@@ -31555,7 +31555,7 @@
         <v>2.77</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31942,10 +31942,10 @@
         <v>69</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF68" t="n">
         <v>2.38</v>
@@ -31975,7 +31975,7 @@
         <v>3.21</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32393,7 +32393,7 @@
         <v>1.13</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -32862,7 +32862,7 @@
         <v>69</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE70" t="n">
         <v>1.13</v>
@@ -33310,10 +33310,10 @@
         <v>63</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE71" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF71" t="n">
         <v>1.38</v>
@@ -33343,7 +33343,7 @@
         <v>2.87</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33758,10 +33758,10 @@
         <v>69</v>
       </c>
       <c r="DD72" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF72" t="n">
         <v>0.75</v>
@@ -33791,7 +33791,7 @@
         <v>2.38</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34230,10 +34230,10 @@
         <v>69</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF73" t="n">
         <v>1.5</v>
@@ -34263,7 +34263,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34670,10 +34670,10 @@
         <v>56</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF74" t="n">
         <v>0.89</v>
@@ -34703,7 +34703,7 @@
         <v>2.43</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35126,10 +35126,10 @@
         <v>67</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF75" t="n">
         <v>1.78</v>
@@ -35159,7 +35159,7 @@
         <v>2.78</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35590,7 +35590,7 @@
         <v>67</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE76" t="n">
         <v>1.13</v>
@@ -36041,7 +36041,7 @@
         <v>1.13</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF77" t="n">
         <v>1.33</v>
@@ -36486,10 +36486,10 @@
         <v>78</v>
       </c>
       <c r="DD78" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF78" t="n">
         <v>0.78</v>
@@ -36519,7 +36519,7 @@
         <v>2.67</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36950,10 +36950,10 @@
         <v>84</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF79" t="n">
         <v>1.33</v>
@@ -36983,7 +36983,7 @@
         <v>2.58</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37406,10 +37406,10 @@
         <v>50</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF80" t="n">
         <v>0.5600000000000001</v>
@@ -37439,7 +37439,7 @@
         <v>2.62</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37862,10 +37862,10 @@
         <v>73</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE81" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF81" t="n">
         <v>1.44</v>
@@ -37895,7 +37895,7 @@
         <v>2.95</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38310,10 +38310,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF82" t="n">
         <v>1.3</v>
@@ -38343,7 +38343,7 @@
         <v>2.62</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -38758,10 +38758,10 @@
         <v>85</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF83" t="n">
         <v>1.5</v>
@@ -38791,7 +38791,7 @@
         <v>2.71</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39222,10 +39222,10 @@
         <v>45</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF84" t="n">
         <v>1.3</v>
@@ -39255,7 +39255,7 @@
         <v>2.33</v>
       </c>
       <c r="DO84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -39670,10 +39670,10 @@
         <v>75</v>
       </c>
       <c r="DD85" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF85" t="n">
         <v>1.9</v>
@@ -39703,7 +39703,7 @@
         <v>3.02</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40134,7 +40134,7 @@
         <v>60</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE86" t="n">
         <v>1.13</v>
@@ -40577,7 +40577,7 @@
         <v>1.13</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF87" t="n">
         <v>0.4</v>
@@ -41022,10 +41022,10 @@
         <v>75</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE88" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -41055,7 +41055,7 @@
         <v>3.04</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41454,10 +41454,10 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF89" t="n">
         <v>2.2</v>
@@ -41487,7 +41487,7 @@
         <v>3.07</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -41918,10 +41918,10 @@
         <v>73</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF90" t="n">
         <v>1.45</v>
@@ -41951,7 +41951,7 @@
         <v>2.56</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42382,10 +42382,10 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF91" t="n">
         <v>0.64</v>
@@ -42415,7 +42415,7 @@
         <v>2.48</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42830,10 +42830,10 @@
         <v>64</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF92" t="n">
         <v>2.36</v>
@@ -42863,7 +42863,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43286,10 +43286,10 @@
         <v>64</v>
       </c>
       <c r="DD93" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF93" t="n">
         <v>0.82</v>
@@ -43319,7 +43319,7 @@
         <v>2.73</v>
       </c>
       <c r="DO93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -43729,7 +43729,7 @@
         <v>1.13</v>
       </c>
       <c r="DE94" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF94" t="n">
         <v>1.27</v>
@@ -44174,10 +44174,10 @@
         <v>73</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF95" t="n">
         <v>1.45</v>
@@ -44207,7 +44207,7 @@
         <v>2.96</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44638,10 +44638,10 @@
         <v>64</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF96" t="n">
         <v>1</v>
@@ -44671,7 +44671,7 @@
         <v>2.41</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45086,7 +45086,7 @@
         <v>78</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE97" t="n">
         <v>1.13</v>
@@ -45542,10 +45542,10 @@
         <v>59</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -45575,7 +45575,7 @@
         <v>2.57</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45977,7 +45977,7 @@
         <v>1.13</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF99" t="n">
         <v>0.67</v>
@@ -46438,10 +46438,10 @@
         <v>88</v>
       </c>
       <c r="DD100" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF100" t="n">
         <v>1.92</v>
@@ -46471,7 +46471,7 @@
         <v>2.84</v>
       </c>
       <c r="DO100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -46886,7 +46886,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE101" t="n">
         <v>1.13</v>
@@ -47334,10 +47334,10 @@
         <v>50</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -47367,7 +47367,7 @@
         <v>2.54</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -47774,10 +47774,10 @@
         <v>75</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE103" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF103" t="n">
         <v>1.17</v>
@@ -47807,7 +47807,7 @@
         <v>2.97</v>
       </c>
       <c r="DO103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48230,10 +48230,10 @@
         <v>83</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF104" t="n">
         <v>1.17</v>
@@ -48263,7 +48263,7 @@
         <v>3.27</v>
       </c>
       <c r="DO104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -48694,10 +48694,10 @@
         <v>71</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF105" t="n">
         <v>1.42</v>
@@ -48727,7 +48727,7 @@
         <v>2.38</v>
       </c>
       <c r="DO105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49161,7 +49161,7 @@
         <v>1.13</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF106" t="n">
         <v>0.6899999999999999</v>
@@ -49606,10 +49606,10 @@
         <v>66</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DE107" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DF107" t="n">
         <v>0.77</v>
@@ -49639,7 +49639,7 @@
         <v>2.74</v>
       </c>
       <c r="DO107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50038,7 +50038,7 @@
         <v>73</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DE108" t="n">
         <v>1.13</v>
@@ -50470,10 +50470,10 @@
         <v>77</v>
       </c>
       <c r="DD109" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DF109" t="n">
         <v>0.77</v>
@@ -50503,7 +50503,7 @@
         <v>2.43</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -50918,10 +50918,10 @@
         <v>54</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DF110" t="n">
         <v>1.08</v>
@@ -50951,7 +50951,7 @@
         <v>2.31</v>
       </c>
       <c r="DO110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -51366,10 +51366,10 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DF111" t="n">
         <v>2.31</v>
@@ -51399,7 +51399,7 @@
         <v>3.1</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -51822,10 +51822,10 @@
         <v>81</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DF112" t="n">
         <v>1.69</v>
@@ -51855,7 +51855,7 @@
         <v>2.94</v>
       </c>
       <c r="DO112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52286,10 +52286,10 @@
         <v>66</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DF113" t="n">
         <v>1.77</v>
@@ -52319,7 +52319,7 @@
         <v>3.09</v>
       </c>
       <c r="DO113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -52734,10 +52734,10 @@
         <v>75</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DF114" t="n">
         <v>1.21</v>
@@ -52767,7 +52767,7 @@
         <v>2.82</v>
       </c>
       <c r="DO114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53185,7 +53185,7 @@
         <v>1.13</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DF115" t="n">
         <v>1.29</v>
@@ -53630,10 +53630,10 @@
         <v>72</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DE116" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -53663,7 +53663,7 @@
         <v>2.89</v>
       </c>
       <c r="DO116" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54078,7 +54078,7 @@
         <v>68</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DE117" t="n">
         <v>1.13</v>
@@ -54518,10 +54518,10 @@
         <v>75</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DE118" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DF118" t="n">
         <v>1.43</v>
@@ -54551,7 +54551,7 @@
         <v>2.65</v>
       </c>
       <c r="DO118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -54982,10 +54982,10 @@
         <v>57</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="DF119" t="n">
         <v>1.36</v>
@@ -55015,7 +55015,7 @@
         <v>2.85</v>
       </c>
       <c r="DO119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -55446,10 +55446,10 @@
         <v>65</v>
       </c>
       <c r="DD120" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DF120" t="n">
         <v>1.86</v>
@@ -55479,7 +55479,7 @@
         <v>2.58</v>
       </c>
       <c r="DO120" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -55878,10 +55878,10 @@
         <v>75</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DF121" t="n">
         <v>1.21</v>
@@ -55911,7 +55911,7 @@
         <v>3.07</v>
       </c>
       <c r="DO121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -56351,7 +56351,7 @@
         <v>2.94</v>
       </c>
       <c r="DO122" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -56771,7 +56771,7 @@
         <v>2.52</v>
       </c>
       <c r="DO123" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -57651,7 +57651,7 @@
         <v>3.19</v>
       </c>
       <c r="DO125" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -58099,7 +58099,7 @@
         <v>2.31</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -58547,7 +58547,7 @@
         <v>2.97</v>
       </c>
       <c r="DO127" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -58995,7 +58995,7 @@
         <v>2.88</v>
       </c>
       <c r="DO128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP128" t="b">
         <v>0</v>
@@ -59539,6 +59539,3158 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>46164.9375</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>3</v>
+      </c>
+      <c r="K130" t="n">
+        <v>7</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10</v>
+      </c>
+      <c r="M130" t="n">
+        <v>6</v>
+      </c>
+      <c r="N130" t="n">
+        <v>3</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1</v>
+      </c>
+      <c r="R130" t="n">
+        <v>3</v>
+      </c>
+      <c r="S130" t="n">
+        <v>9</v>
+      </c>
+      <c r="T130" t="n">
+        <v>9</v>
+      </c>
+      <c r="U130" t="n">
+        <v>10</v>
+      </c>
+      <c r="V130" t="n">
+        <v>12</v>
+      </c>
+      <c r="W130" t="n">
+        <v>18</v>
+      </c>
+      <c r="X130" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>75</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW130" t="inlineStr"/>
+      <c r="DX130" t="inlineStr"/>
+      <c r="DY130" t="inlineStr"/>
+      <c r="DZ130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr"/>
+      <c r="EH130" t="inlineStr"/>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr"/>
+      <c r="EL130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>46165.54166666666</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9</v>
+      </c>
+      <c r="M131" t="n">
+        <v>6</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>2</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" t="n">
+        <v>6</v>
+      </c>
+      <c r="W131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>Parque Abraham Paladino</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>Avenida Emilio Romero, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW131" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX131" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="ED131" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EF131" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EG131" t="inlineStr"/>
+      <c r="EH131" t="inlineStr"/>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>46165.75</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4</v>
+      </c>
+      <c r="L132" t="n">
+        <v>5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>4</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>4</v>
+      </c>
+      <c r="T132" t="n">
+        <v>7</v>
+      </c>
+      <c r="U132" t="n">
+        <v>8</v>
+      </c>
+      <c r="V132" t="n">
+        <v>8</v>
+      </c>
+      <c r="W132" t="n">
+        <v>2</v>
+      </c>
+      <c r="X132" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>4371</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DX132" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr"/>
+      <c r="EH132" t="inlineStr"/>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>46165.89583333334</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>13</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>13</v>
+      </c>
+      <c r="M133" t="n">
+        <v>4</v>
+      </c>
+      <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>6</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>6</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" t="n">
+        <v>12</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>Estadio Gran Parque Central</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>98</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW133" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="DX133" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="ED133" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr"/>
+      <c r="EI133" t="inlineStr"/>
+      <c r="EJ133" t="inlineStr"/>
+      <c r="EK133" t="inlineStr"/>
+      <c r="EL133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>5</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
+      </c>
+      <c r="U134" t="n">
+        <v>6</v>
+      </c>
+      <c r="V134" t="n">
+        <v>4</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Estadio Monumental Luis Tróccoli</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>4360</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>51</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>38</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>69</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>51</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW134" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DX134" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr"/>
+      <c r="EH134" t="inlineStr"/>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr"/>
+      <c r="EL134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>46166.75</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>6</v>
+      </c>
+      <c r="L135" t="n">
+        <v>11</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2</v>
+      </c>
+      <c r="R135" t="n">
+        <v>4</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>3</v>
+      </c>
+      <c r="U135" t="n">
+        <v>7</v>
+      </c>
+      <c r="V135" t="n">
+        <v>7</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Parque Alfredo Víctor Viera</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW135" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DX135" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr"/>
+      <c r="EH135" t="inlineStr"/>
+      <c r="EI135" t="inlineStr"/>
+      <c r="EJ135" t="inlineStr"/>
+      <c r="EK135" t="inlineStr"/>
+      <c r="EL135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3</v>
+      </c>
+      <c r="S136" t="n">
+        <v>8</v>
+      </c>
+      <c r="T136" t="n">
+        <v>3</v>
+      </c>
+      <c r="U136" t="n">
+        <v>12</v>
+      </c>
+      <c r="V136" t="n">
+        <v>6</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Estadio Luis Franzini</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>4358</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW136" t="inlineStr"/>
+      <c r="DX136" t="inlineStr"/>
+      <c r="DY136" t="inlineStr"/>
+      <c r="DZ136" t="inlineStr"/>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr"/>
+      <c r="EH136" t="inlineStr"/>
+      <c r="EI136" t="inlineStr"/>
+      <c r="EJ136" t="inlineStr"/>
+      <c r="EK136" t="inlineStr"/>
+      <c r="EL136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL136" headerRowCount="1">
-  <autoFilter ref="A1:EL136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL144" headerRowCount="1">
+  <autoFilter ref="A1:EL144"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL136"/>
+  <dimension ref="A1:EL144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -597,8 +597,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="50" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="16.8" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -1514,16 +1514,8 @@
       <c r="Z2" t="n">
         <v>36</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>6</v>
       </c>
@@ -1762,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1795,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1970,16 +1962,8 @@
       <c r="Z3" t="n">
         <v>54</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
@@ -2218,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2251,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2426,16 +2410,8 @@
       <c r="Z4" t="n">
         <v>40</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>8</v>
       </c>
@@ -2674,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2707,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2890,16 +2866,8 @@
       <c r="Z5" t="n">
         <v>55</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
@@ -3138,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3171,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3362,16 +3330,8 @@
       <c r="Z6" t="n">
         <v>42</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>2</v>
       </c>
@@ -3610,10 +3570,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3643,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3802,16 +3762,8 @@
       <c r="Z7" t="n">
         <v>47</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>1</v>
       </c>
@@ -4050,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4083,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4258,16 +4210,8 @@
       <c r="Z8" t="n">
         <v>57</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>4</v>
       </c>
@@ -4506,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4539,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4678,16 +4622,8 @@
       <c r="Z9" t="n">
         <v>64</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
@@ -4926,10 +4862,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4959,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5126,16 +5062,8 @@
       <c r="Z10" t="n">
         <v>45</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
         <v>3</v>
       </c>
@@ -5374,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5407,7 +5335,7 @@
         <v>3.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5590,16 +5518,8 @@
       <c r="Z11" t="n">
         <v>46</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>1</v>
       </c>
@@ -5838,10 +5758,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5871,7 +5791,7 @@
         <v>2.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6062,16 +5982,8 @@
       <c r="Z12" t="n">
         <v>42</v>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
@@ -6310,10 +6222,10 @@
         <v>100</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6343,7 +6255,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6518,16 +6430,8 @@
       <c r="Z13" t="n">
         <v>34</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>4</v>
       </c>
@@ -6766,10 +6670,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6799,7 +6703,7 @@
         <v>2.94</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6938,16 +6842,8 @@
       <c r="Z14" t="n">
         <v>38</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
@@ -7186,10 +7082,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7219,7 +7115,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7402,16 +7298,8 @@
       <c r="Z15" t="n">
         <v>70</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>2</v>
       </c>
@@ -7650,10 +7538,10 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7683,7 +7571,7 @@
         <v>2.66</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7874,16 +7762,8 @@
       <c r="Z16" t="n">
         <v>43</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>4</v>
       </c>
@@ -8122,10 +8002,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8155,7 +8035,7 @@
         <v>2.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8578,10 +8458,10 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8611,7 +8491,7 @@
         <v>3.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8802,16 +8682,8 @@
       <c r="Z18" t="n">
         <v>65</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>5</v>
       </c>
@@ -9050,10 +8922,10 @@
         <v>75</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9083,7 +8955,7 @@
         <v>2.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9250,16 +9122,8 @@
       <c r="Z19" t="n">
         <v>45</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
         <v>2</v>
       </c>
@@ -9498,10 +9362,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF19" t="n">
         <v>2</v>
@@ -9531,7 +9395,7 @@
         <v>2.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9706,16 +9570,8 @@
       <c r="Z20" t="n">
         <v>54</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
         <v>3</v>
       </c>
@@ -9954,10 +9810,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -9987,7 +9843,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10162,16 +10018,8 @@
       <c r="Z21" t="n">
         <v>57</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
         <v>3</v>
       </c>
@@ -10410,10 +10258,10 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10443,7 +10291,7 @@
         <v>2.35</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>0</v>
@@ -10610,16 +10458,8 @@
       <c r="Z22" t="n">
         <v>67</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>4</v>
       </c>
@@ -10858,10 +10698,10 @@
         <v>75</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -10891,7 +10731,7 @@
         <v>2.43</v>
       </c>
       <c r="DO22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11066,16 +10906,8 @@
       <c r="Z23" t="n">
         <v>44</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>1</v>
       </c>
@@ -11314,10 +11146,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF23" t="n">
         <v>2</v>
@@ -11347,7 +11179,7 @@
         <v>3.26</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11522,16 +11354,8 @@
       <c r="Z24" t="n">
         <v>37</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>4</v>
       </c>
@@ -11770,10 +11594,10 @@
         <v>75</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF24" t="n">
         <v>0.5</v>
@@ -11803,7 +11627,7 @@
         <v>3.18</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11986,16 +11810,8 @@
       <c r="Z25" t="n">
         <v>46</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>2</v>
       </c>
@@ -12234,10 +12050,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12267,7 +12083,7 @@
         <v>2.78</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12666,10 +12482,10 @@
         <v>84</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF26" t="n">
         <v>1.33</v>
@@ -12699,7 +12515,7 @@
         <v>2.98</v>
       </c>
       <c r="DO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12874,16 +12690,8 @@
       <c r="Z27" t="n">
         <v>62</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>2</v>
       </c>
@@ -13122,10 +12930,10 @@
         <v>17</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF27" t="n">
         <v>0.33</v>
@@ -13155,7 +12963,7 @@
         <v>2.23</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13330,16 +13138,8 @@
       <c r="Z28" t="n">
         <v>36</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>3</v>
       </c>
@@ -13578,10 +13378,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF28" t="n">
         <v>1.33</v>
@@ -13611,7 +13411,7 @@
         <v>3.23</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13778,16 +13578,8 @@
       <c r="Z29" t="n">
         <v>39</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
@@ -14026,10 +13818,10 @@
         <v>67</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF29" t="n">
         <v>2</v>
@@ -14059,7 +13851,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14250,16 +14042,8 @@
       <c r="Z30" t="n">
         <v>59</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>2</v>
       </c>
@@ -14498,10 +14282,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14531,7 +14315,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14698,16 +14482,8 @@
       <c r="Z31" t="n">
         <v>46</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
@@ -14946,10 +14722,10 @@
         <v>67</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -14979,7 +14755,7 @@
         <v>2.56</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15170,16 +14946,8 @@
       <c r="Z32" t="n">
         <v>42</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>3</v>
       </c>
@@ -15418,10 +15186,10 @@
         <v>67</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF32" t="n">
         <v>2.33</v>
@@ -15451,7 +15219,7 @@
         <v>2.54</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15642,16 +15410,8 @@
       <c r="Z33" t="n">
         <v>36</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>2</v>
       </c>
@@ -15890,10 +15650,10 @@
         <v>84</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF33" t="n">
         <v>2</v>
@@ -15923,7 +15683,7 @@
         <v>3.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16098,16 +15858,8 @@
       <c r="Z34" t="n">
         <v>56</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>8</v>
       </c>
@@ -16346,10 +16098,10 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF34" t="n">
         <v>1.75</v>
@@ -16379,7 +16131,7 @@
         <v>2.89</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>0</v>
@@ -16538,16 +16290,8 @@
       <c r="Z35" t="n">
         <v>47</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>3</v>
       </c>
@@ -16786,10 +16530,10 @@
         <v>88</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF35" t="n">
         <v>0.25</v>
@@ -16819,7 +16563,7 @@
         <v>2.13</v>
       </c>
       <c r="DO35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -16994,16 +16738,8 @@
       <c r="Z36" t="n">
         <v>43</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>1</v>
       </c>
@@ -17242,10 +16978,10 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF36" t="n">
         <v>2.25</v>
@@ -17275,7 +17011,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17450,16 +17186,8 @@
       <c r="Z37" t="n">
         <v>46</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>4</v>
       </c>
@@ -17698,10 +17426,10 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF37" t="n">
         <v>1.75</v>
@@ -17731,7 +17459,7 @@
         <v>3</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17906,16 +17634,8 @@
       <c r="Z38" t="n">
         <v>64</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>5</v>
       </c>
@@ -18154,10 +17874,10 @@
         <v>63</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF38" t="n">
         <v>0.25</v>
@@ -18187,7 +17907,7 @@
         <v>2.91</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18362,16 +18082,8 @@
       <c r="Z39" t="n">
         <v>35</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>2</v>
       </c>
@@ -18610,10 +18322,10 @@
         <v>50</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF39" t="n">
         <v>1.75</v>
@@ -18643,7 +18355,7 @@
         <v>2.59</v>
       </c>
       <c r="DO39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -18802,16 +18514,8 @@
       <c r="Z40" t="n">
         <v>57</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>4</v>
       </c>
@@ -19050,10 +18754,10 @@
         <v>88</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF40" t="n">
         <v>0.75</v>
@@ -19083,7 +18787,7 @@
         <v>2.4</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19258,16 +18962,8 @@
       <c r="Z41" t="n">
         <v>46</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>5</v>
       </c>
@@ -19506,10 +19202,10 @@
         <v>50</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF41" t="n">
         <v>0.5</v>
@@ -19539,7 +19235,7 @@
         <v>2.21</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19722,16 +19418,8 @@
       <c r="Z42" t="n">
         <v>44</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>3</v>
       </c>
@@ -19970,10 +19658,10 @@
         <v>60</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -20003,7 +19691,7 @@
         <v>2.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20142,16 +19830,8 @@
       <c r="Z43" t="n">
         <v>52</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>4</v>
       </c>
@@ -20390,10 +20070,10 @@
         <v>70</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF43" t="n">
         <v>0.4</v>
@@ -20423,7 +20103,7 @@
         <v>2.19</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20606,16 +20286,8 @@
       <c r="Z44" t="n">
         <v>52</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>2</v>
       </c>
@@ -20854,10 +20526,10 @@
         <v>60</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE44" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF44" t="n">
         <v>0.4</v>
@@ -20887,7 +20559,7 @@
         <v>2.6</v>
       </c>
       <c r="DO44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21070,16 +20742,8 @@
       <c r="Z45" t="n">
         <v>50</v>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
         <v>4</v>
       </c>
@@ -21318,10 +20982,10 @@
         <v>70</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF45" t="n">
         <v>1</v>
@@ -21351,7 +21015,7 @@
         <v>2.63</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21534,16 +21198,8 @@
       <c r="Z46" t="n">
         <v>54</v>
       </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
         <v>2</v>
       </c>
@@ -21782,10 +21438,10 @@
         <v>40</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -21815,7 +21471,7 @@
         <v>2.41</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21998,16 +21654,8 @@
       <c r="Z47" t="n">
         <v>40</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>1</v>
       </c>
@@ -22246,10 +21894,10 @@
         <v>70</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF47" t="n">
         <v>2</v>
@@ -22279,7 +21927,7 @@
         <v>3.06</v>
       </c>
       <c r="DO47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22454,16 +22102,8 @@
       <c r="Z48" t="n">
         <v>52</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>5</v>
       </c>
@@ -22702,10 +22342,10 @@
         <v>70</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF48" t="n">
         <v>1.6</v>
@@ -22735,7 +22375,7 @@
         <v>2.61</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -22910,16 +22550,8 @@
       <c r="Z49" t="n">
         <v>60</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>2</v>
       </c>
@@ -23158,10 +22790,10 @@
         <v>80</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF49" t="n">
         <v>2</v>
@@ -23191,7 +22823,7 @@
         <v>2.59</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>0</v>
@@ -23366,16 +22998,8 @@
       <c r="Z50" t="n">
         <v>49</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>3</v>
       </c>
@@ -23614,10 +23238,10 @@
         <v>67</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -23647,7 +23271,7 @@
         <v>2.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -23838,16 +23462,8 @@
       <c r="Z51" t="n">
         <v>46</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>1</v>
       </c>
@@ -24086,10 +23702,10 @@
         <v>59</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24119,7 +23735,7 @@
         <v>2.88</v>
       </c>
       <c r="DO51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24310,16 +23926,8 @@
       <c r="Z52" t="n">
         <v>56</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>2</v>
       </c>
@@ -24558,10 +24166,10 @@
         <v>67</v>
       </c>
       <c r="DD52" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
         <v>2.17</v>
@@ -24591,7 +24199,7 @@
         <v>3.02</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24766,16 +24374,8 @@
       <c r="Z53" t="n">
         <v>41</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Parque Federico Omar Saroldi</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>Avenida 19 de Abril 1145 entre Atilio Pelossi y Lucas Obes, Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
         <v>4</v>
       </c>
@@ -25014,10 +24614,10 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF53" t="n">
         <v>1.83</v>
@@ -25047,7 +24647,7 @@
         <v>2.55</v>
       </c>
       <c r="DO53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25238,16 +24838,8 @@
       <c r="Z54" t="n">
         <v>56</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>4</v>
       </c>
@@ -25486,10 +25078,10 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF54" t="n">
         <v>1.33</v>
@@ -25519,7 +25111,7 @@
         <v>2.47</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25702,16 +25294,8 @@
       <c r="Z55" t="n">
         <v>29</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
         <v>5</v>
       </c>
@@ -25950,10 +25534,10 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF55" t="n">
         <v>2.17</v>
@@ -25983,7 +25567,7 @@
         <v>2.62</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26174,16 +25758,8 @@
       <c r="Z56" t="n">
         <v>41</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
@@ -26422,10 +25998,10 @@
         <v>83</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF56" t="n">
         <v>0.67</v>
@@ -26455,7 +26031,7 @@
         <v>2.67</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -26630,16 +26206,8 @@
       <c r="Z57" t="n">
         <v>43</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>4</v>
       </c>
@@ -26878,10 +26446,10 @@
         <v>58</v>
       </c>
       <c r="DD57" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF57" t="n">
         <v>0.83</v>
@@ -26911,7 +26479,7 @@
         <v>1.94</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27102,16 +26670,8 @@
       <c r="Z58" t="n">
         <v>48</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>1</v>
       </c>
@@ -27350,10 +26910,10 @@
         <v>71</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF58" t="n">
         <v>1.86</v>
@@ -27383,7 +26943,7 @@
         <v>2.88</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27574,16 +27134,8 @@
       <c r="Z59" t="n">
         <v>32</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
         <v>4</v>
       </c>
@@ -27822,10 +27374,10 @@
         <v>50</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF59" t="n">
         <v>1.57</v>
@@ -27855,7 +27407,7 @@
         <v>2.65</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28046,16 +27598,8 @@
       <c r="Z60" t="n">
         <v>48</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
         <v>1</v>
       </c>
@@ -28294,10 +27838,10 @@
         <v>71</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF60" t="n">
         <v>1.43</v>
@@ -28327,7 +27871,7 @@
         <v>2.74</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28518,16 +28062,8 @@
       <c r="Z61" t="n">
         <v>53</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>5</v>
       </c>
@@ -28766,10 +28302,10 @@
         <v>79</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF61" t="n">
         <v>1.14</v>
@@ -28799,7 +28335,7 @@
         <v>2.46</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -28974,16 +28510,8 @@
       <c r="Z62" t="n">
         <v>58</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
         <v>4</v>
       </c>
@@ -29222,10 +28750,10 @@
         <v>65</v>
       </c>
       <c r="DD62" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF62" t="n">
         <v>0.29</v>
@@ -29255,7 +28783,7 @@
         <v>2.66</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29438,16 +28966,8 @@
       <c r="Z63" t="n">
         <v>45</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
@@ -29686,10 +29206,10 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF63" t="n">
         <v>0.71</v>
@@ -29719,7 +29239,7 @@
         <v>2.42</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -29898,16 +29418,8 @@
       <c r="Z64" t="n">
         <v>46</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>4</v>
       </c>
@@ -30146,10 +29658,10 @@
         <v>64</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF64" t="n">
         <v>2.29</v>
@@ -30179,7 +29691,7 @@
         <v>2.65</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30370,16 +29882,8 @@
       <c r="Z65" t="n">
         <v>42</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
         <v>1</v>
       </c>
@@ -30618,10 +30122,10 @@
         <v>64</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF65" t="n">
         <v>1.57</v>
@@ -30651,7 +30155,7 @@
         <v>2.62</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -30834,16 +30338,8 @@
       <c r="Z66" t="n">
         <v>52</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
         <v>2</v>
       </c>
@@ -31082,10 +30578,10 @@
         <v>57</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF66" t="n">
         <v>1.38</v>
@@ -31115,7 +30611,7 @@
         <v>2.78</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31522,10 +31018,10 @@
         <v>75</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF67" t="n">
         <v>1.75</v>
@@ -31555,7 +31051,7 @@
         <v>2.77</v>
       </c>
       <c r="DO67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -31694,16 +31190,8 @@
       <c r="Z68" t="n">
         <v>36</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
         <v>3</v>
       </c>
@@ -31942,10 +31430,10 @@
         <v>69</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF68" t="n">
         <v>2.38</v>
@@ -31975,7 +31463,7 @@
         <v>3.21</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32142,16 +31630,8 @@
       <c r="Z69" t="n">
         <v>48</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
         <v>5</v>
       </c>
@@ -32390,10 +31870,10 @@
         <v>57</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -32423,7 +31903,7 @@
         <v>2.31</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -32614,16 +32094,8 @@
       <c r="Z70" t="n">
         <v>52</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
         <v>3</v>
       </c>
@@ -32862,10 +32334,10 @@
         <v>69</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF70" t="n">
         <v>1.13</v>
@@ -32895,7 +32367,7 @@
         <v>2.45</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33062,16 +32534,8 @@
       <c r="Z71" t="n">
         <v>60</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>6</v>
       </c>
@@ -33310,10 +32774,10 @@
         <v>63</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF71" t="n">
         <v>1.38</v>
@@ -33343,7 +32807,7 @@
         <v>2.87</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33510,16 +32974,8 @@
       <c r="Z72" t="n">
         <v>48</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
         <v>3</v>
       </c>
@@ -33758,10 +33214,10 @@
         <v>69</v>
       </c>
       <c r="DD72" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF72" t="n">
         <v>0.75</v>
@@ -33791,7 +33247,7 @@
         <v>2.38</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -33982,16 +33438,8 @@
       <c r="Z73" t="n">
         <v>55</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
         <v>4</v>
       </c>
@@ -34230,10 +33678,10 @@
         <v>69</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF73" t="n">
         <v>1.5</v>
@@ -34263,7 +33711,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34422,16 +33870,8 @@
       <c r="Z74" t="n">
         <v>53</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
         <v>2</v>
       </c>
@@ -34670,10 +34110,10 @@
         <v>56</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF74" t="n">
         <v>0.89</v>
@@ -34703,7 +34143,7 @@
         <v>2.43</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34878,16 +34318,8 @@
       <c r="Z75" t="n">
         <v>34</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>2</v>
       </c>
@@ -35126,10 +34558,10 @@
         <v>67</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF75" t="n">
         <v>1.78</v>
@@ -35159,7 +34591,7 @@
         <v>2.78</v>
       </c>
       <c r="DO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35342,16 +34774,8 @@
       <c r="Z76" t="n">
         <v>62</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
@@ -35590,10 +35014,10 @@
         <v>67</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF76" t="n">
         <v>2.22</v>
@@ -35623,7 +35047,7 @@
         <v>3.03</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -35790,16 +35214,8 @@
       <c r="Z77" t="n">
         <v>49</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>4</v>
       </c>
@@ -36038,10 +35454,10 @@
         <v>73</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF77" t="n">
         <v>1.33</v>
@@ -36071,7 +35487,7 @@
         <v>2.56</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36486,10 +35902,10 @@
         <v>78</v>
       </c>
       <c r="DD78" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF78" t="n">
         <v>0.78</v>
@@ -36519,7 +35935,7 @@
         <v>2.67</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -36702,16 +36118,8 @@
       <c r="Z79" t="n">
         <v>59</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>3</v>
       </c>
@@ -36950,10 +36358,10 @@
         <v>84</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF79" t="n">
         <v>1.33</v>
@@ -36983,7 +36391,7 @@
         <v>2.58</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37158,16 +36566,8 @@
       <c r="Z80" t="n">
         <v>57</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
@@ -37406,10 +36806,10 @@
         <v>50</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF80" t="n">
         <v>0.5600000000000001</v>
@@ -37439,7 +36839,7 @@
         <v>2.62</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37614,16 +37014,8 @@
       <c r="Z81" t="n">
         <v>44</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>4</v>
       </c>
@@ -37862,10 +37254,10 @@
         <v>73</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF81" t="n">
         <v>1.44</v>
@@ -37895,7 +37287,7 @@
         <v>2.95</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38062,16 +37454,8 @@
       <c r="Z82" t="n">
         <v>49</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
         <v>2</v>
       </c>
@@ -38310,10 +37694,10 @@
         <v>60</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF82" t="n">
         <v>1.3</v>
@@ -38343,7 +37727,7 @@
         <v>2.62</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -38758,10 +38142,10 @@
         <v>85</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF83" t="n">
         <v>1.5</v>
@@ -38791,7 +38175,7 @@
         <v>2.71</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -38974,16 +38358,8 @@
       <c r="Z84" t="n">
         <v>41</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>2</v>
       </c>
@@ -39222,10 +38598,10 @@
         <v>45</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF84" t="n">
         <v>1.3</v>
@@ -39255,7 +38631,7 @@
         <v>2.33</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -39422,16 +38798,8 @@
       <c r="Z85" t="n">
         <v>52</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
         <v>4</v>
       </c>
@@ -39670,10 +39038,10 @@
         <v>75</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF85" t="n">
         <v>1.9</v>
@@ -39703,7 +39071,7 @@
         <v>3.02</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -39886,16 +39254,8 @@
       <c r="Z86" t="n">
         <v>59</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>5</v>
       </c>
@@ -40134,10 +39494,10 @@
         <v>60</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF86" t="n">
         <v>1.7</v>
@@ -40167,7 +39527,7 @@
         <v>2.5</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40326,16 +39686,8 @@
       <c r="Z87" t="n">
         <v>40</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
         <v>3</v>
       </c>
@@ -40574,10 +39926,10 @@
         <v>75</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF87" t="n">
         <v>0.4</v>
@@ -40607,7 +39959,7 @@
         <v>2.44</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -40774,16 +40126,8 @@
       <c r="Z88" t="n">
         <v>62</v>
       </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
         <v>3</v>
       </c>
@@ -41022,10 +40366,10 @@
         <v>75</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE88" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF88" t="n">
         <v>1.4</v>
@@ -41055,7 +40399,7 @@
         <v>3.04</v>
       </c>
       <c r="DO88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41206,16 +40550,8 @@
       <c r="Z89" t="n">
         <v>36</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
         <v>4</v>
       </c>
@@ -41454,10 +40790,10 @@
         <v>75</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF89" t="n">
         <v>2.2</v>
@@ -41487,7 +40823,7 @@
         <v>3.07</v>
       </c>
       <c r="DO89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -41670,16 +41006,8 @@
       <c r="Z90" t="n">
         <v>32</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
         <v>1</v>
       </c>
@@ -41918,10 +41246,10 @@
         <v>73</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF90" t="n">
         <v>1.45</v>
@@ -41951,7 +41279,7 @@
         <v>2.56</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42134,16 +41462,8 @@
       <c r="Z91" t="n">
         <v>52</v>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
         <v>2</v>
       </c>
@@ -42382,10 +41702,10 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF91" t="n">
         <v>0.64</v>
@@ -42415,7 +41735,7 @@
         <v>2.48</v>
       </c>
       <c r="DO91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42582,16 +41902,8 @@
       <c r="Z92" t="n">
         <v>53</v>
       </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
         <v>2</v>
       </c>
@@ -42830,10 +42142,10 @@
         <v>64</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF92" t="n">
         <v>2.36</v>
@@ -42863,7 +42175,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43038,16 +42350,8 @@
       <c r="Z93" t="n">
         <v>59</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
         <v>2</v>
       </c>
@@ -43286,10 +42590,10 @@
         <v>64</v>
       </c>
       <c r="DD93" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF93" t="n">
         <v>0.82</v>
@@ -43319,7 +42623,7 @@
         <v>2.73</v>
       </c>
       <c r="DO93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -43478,16 +42782,8 @@
       <c r="Z94" t="n">
         <v>54</v>
       </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>1</v>
       </c>
@@ -43726,10 +43022,10 @@
         <v>78</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF94" t="n">
         <v>1.27</v>
@@ -43759,7 +43055,7 @@
         <v>2.66</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44174,10 +43470,10 @@
         <v>73</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF95" t="n">
         <v>1.45</v>
@@ -44207,7 +43503,7 @@
         <v>2.96</v>
       </c>
       <c r="DO95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44390,16 +43686,8 @@
       <c r="Z96" t="n">
         <v>51</v>
       </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
         <v>3</v>
       </c>
@@ -44638,10 +43926,10 @@
         <v>64</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF96" t="n">
         <v>1</v>
@@ -44671,7 +43959,7 @@
         <v>2.41</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -44838,16 +44126,8 @@
       <c r="Z97" t="n">
         <v>53</v>
       </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
         <v>5</v>
       </c>
@@ -45086,10 +44366,10 @@
         <v>78</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF97" t="n">
         <v>2</v>
@@ -45119,7 +44399,7 @@
         <v>3.16</v>
       </c>
       <c r="DO97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -45542,10 +44822,10 @@
         <v>59</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF98" t="n">
         <v>1.33</v>
@@ -45575,7 +44855,7 @@
         <v>2.57</v>
       </c>
       <c r="DO98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -45726,16 +45006,8 @@
       <c r="Z99" t="n">
         <v>40</v>
       </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
         <v>4</v>
       </c>
@@ -45974,10 +45246,10 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF99" t="n">
         <v>0.67</v>
@@ -46007,7 +45279,7 @@
         <v>2.77</v>
       </c>
       <c r="DO99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46190,16 +45462,8 @@
       <c r="Z100" t="n">
         <v>50</v>
       </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="n">
         <v>3</v>
       </c>
@@ -46438,10 +45702,10 @@
         <v>88</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF100" t="n">
         <v>1.92</v>
@@ -46471,7 +45735,7 @@
         <v>2.84</v>
       </c>
       <c r="DO100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -46638,16 +45902,8 @@
       <c r="Z101" t="n">
         <v>45</v>
       </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
@@ -46886,10 +46142,10 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF101" t="n">
         <v>1.58</v>
@@ -46919,7 +46175,7 @@
         <v>2.81</v>
       </c>
       <c r="DO101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47086,16 +46342,8 @@
       <c r="Z102" t="n">
         <v>55</v>
       </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="n">
         <v>4</v>
       </c>
@@ -47334,10 +46582,10 @@
         <v>50</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -47367,7 +46615,7 @@
         <v>2.54</v>
       </c>
       <c r="DO102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -47526,16 +46774,8 @@
       <c r="Z103" t="n">
         <v>51</v>
       </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="n">
         <v>3</v>
       </c>
@@ -47774,10 +47014,10 @@
         <v>75</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE103" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF103" t="n">
         <v>1.17</v>
@@ -47807,7 +47047,7 @@
         <v>2.97</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -47982,16 +47222,8 @@
       <c r="Z104" t="n">
         <v>61</v>
       </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="n">
         <v>4</v>
       </c>
@@ -48230,10 +47462,10 @@
         <v>83</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF104" t="n">
         <v>1.17</v>
@@ -48263,7 +47495,7 @@
         <v>3.27</v>
       </c>
       <c r="DO104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -48446,16 +47678,8 @@
       <c r="Z105" t="n">
         <v>35</v>
       </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="n">
         <v>5</v>
       </c>
@@ -48694,10 +47918,10 @@
         <v>71</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF105" t="n">
         <v>1.42</v>
@@ -48727,7 +47951,7 @@
         <v>2.38</v>
       </c>
       <c r="DO105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48910,16 +48134,8 @@
       <c r="Z106" t="n">
         <v>46</v>
       </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="n">
         <v>4</v>
       </c>
@@ -49158,10 +48374,10 @@
         <v>77</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DF106" t="n">
         <v>0.6899999999999999</v>
@@ -49191,7 +48407,7 @@
         <v>2.94</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49358,16 +48574,8 @@
       <c r="Z107" t="n">
         <v>59</v>
       </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
@@ -49606,10 +48814,10 @@
         <v>66</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DF107" t="n">
         <v>0.77</v>
@@ -49639,7 +48847,7 @@
         <v>2.74</v>
       </c>
       <c r="DO107" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -49790,16 +48998,8 @@
       <c r="Z108" t="n">
         <v>52</v>
       </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="n">
         <v>1</v>
       </c>
@@ -50038,10 +49238,10 @@
         <v>73</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF108" t="n">
         <v>1.31</v>
@@ -50071,7 +49271,7 @@
         <v>2.57</v>
       </c>
       <c r="DO108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -50222,16 +49422,8 @@
       <c r="Z109" t="n">
         <v>43</v>
       </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
         <v>3</v>
       </c>
@@ -50470,10 +49662,10 @@
         <v>77</v>
       </c>
       <c r="DD109" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DF109" t="n">
         <v>0.77</v>
@@ -50503,7 +49695,7 @@
         <v>2.43</v>
       </c>
       <c r="DO109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -50670,16 +49862,8 @@
       <c r="Z110" t="n">
         <v>42</v>
       </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
         <v>1</v>
       </c>
@@ -50918,10 +50102,10 @@
         <v>54</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DF110" t="n">
         <v>1.08</v>
@@ -50951,7 +50135,7 @@
         <v>2.31</v>
       </c>
       <c r="DO110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -51118,16 +50302,8 @@
       <c r="Z111" t="n">
         <v>62</v>
       </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="n">
         <v>3</v>
       </c>
@@ -51366,10 +50542,10 @@
         <v>77</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DF111" t="n">
         <v>2.31</v>
@@ -51399,7 +50575,7 @@
         <v>3.1</v>
       </c>
       <c r="DO111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -51822,10 +50998,10 @@
         <v>81</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DF112" t="n">
         <v>1.69</v>
@@ -51855,7 +51031,7 @@
         <v>2.94</v>
       </c>
       <c r="DO112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52038,16 +51214,8 @@
       <c r="Z113" t="n">
         <v>60</v>
       </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="n">
         <v>7</v>
       </c>
@@ -52286,10 +51454,10 @@
         <v>66</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DF113" t="n">
         <v>1.77</v>
@@ -52319,7 +51487,7 @@
         <v>3.09</v>
       </c>
       <c r="DO113" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -52486,16 +51654,8 @@
       <c r="Z114" t="n">
         <v>60</v>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="n">
         <v>2</v>
       </c>
@@ -52734,10 +51894,10 @@
         <v>75</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="DF114" t="n">
         <v>1.21</v>
@@ -52767,7 +51927,7 @@
         <v>2.82</v>
       </c>
       <c r="DO114" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -52934,16 +52094,8 @@
       <c r="Z115" t="n">
         <v>52</v>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Estadio Jardines del Hipódromo</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Carlos Nery esq. Avenida Acrópolis, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>5</v>
       </c>
@@ -53182,10 +52334,10 @@
         <v>79</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DF115" t="n">
         <v>1.29</v>
@@ -53215,7 +52367,7 @@
         <v>2.54</v>
       </c>
       <c r="DO115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -53382,16 +52534,8 @@
       <c r="Z116" t="n">
         <v>66</v>
       </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="n">
         <v>3</v>
       </c>
@@ -53630,10 +52774,10 @@
         <v>72</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DE116" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DF116" t="n">
         <v>1.5</v>
@@ -53663,7 +52807,7 @@
         <v>2.89</v>
       </c>
       <c r="DO116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -53830,16 +52974,8 @@
       <c r="Z117" t="n">
         <v>47</v>
       </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="n">
         <v>5</v>
       </c>
@@ -54078,10 +53214,10 @@
         <v>68</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DF117" t="n">
         <v>1.5</v>
@@ -54111,7 +53247,7 @@
         <v>2.85</v>
       </c>
       <c r="DO117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -54518,10 +53654,10 @@
         <v>75</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DE118" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="DF118" t="n">
         <v>1.43</v>
@@ -54551,7 +53687,7 @@
         <v>2.65</v>
       </c>
       <c r="DO118" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -54734,16 +53870,8 @@
       <c r="Z119" t="n">
         <v>46</v>
       </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="n">
         <v>1</v>
       </c>
@@ -54982,10 +54110,10 @@
         <v>57</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DE119" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DF119" t="n">
         <v>1.36</v>
@@ -55015,7 +54143,7 @@
         <v>2.85</v>
       </c>
       <c r="DO119" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -55198,16 +54326,8 @@
       <c r="Z120" t="n">
         <v>47</v>
       </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="n">
         <v>2</v>
       </c>
@@ -55446,10 +54566,10 @@
         <v>65</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF120" t="n">
         <v>1.86</v>
@@ -55479,7 +54599,7 @@
         <v>2.58</v>
       </c>
       <c r="DO120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -55630,16 +54750,8 @@
       <c r="Z121" t="n">
         <v>50</v>
       </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="n">
         <v>1</v>
       </c>
@@ -55878,10 +54990,10 @@
         <v>75</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DF121" t="n">
         <v>1.21</v>
@@ -55911,7 +55023,7 @@
         <v>3.07</v>
       </c>
       <c r="DO121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -56321,7 +55433,7 @@
         <v>1.63</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF122" t="n">
         <v>1.86</v>
@@ -56351,7 +55463,7 @@
         <v>2.94</v>
       </c>
       <c r="DO122" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -56490,16 +55602,8 @@
       <c r="Z123" t="n">
         <v>40</v>
       </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>Parque José Nasazzi</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>Avenida Leon Ribeiro, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="n">
         <v>2</v>
       </c>
@@ -56738,10 +55842,10 @@
         <v>68</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="DF123" t="n">
         <v>1.25</v>
@@ -56771,7 +55875,7 @@
         <v>2.52</v>
       </c>
       <c r="DO123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -56938,16 +56042,8 @@
       <c r="Z124" t="n">
         <v>53</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Parque Artigas</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Avenida José Artigas S/N y Blandengues, Las Piedras</t>
-        </is>
-      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="n">
         <v>1</v>
       </c>
@@ -57186,10 +56282,10 @@
         <v>73</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DF124" t="n">
         <v>1.25</v>
@@ -57219,7 +56315,7 @@
         <v>2.79</v>
       </c>
       <c r="DO124" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -57370,16 +56466,8 @@
       <c r="Z125" t="n">
         <v>56</v>
       </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>Estadio Campeón del Siglo</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>Camino de los Siete Cerros, Vila Don Bosco, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="n">
         <v>4</v>
       </c>
@@ -57618,10 +56706,10 @@
         <v>88</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DE125" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF125" t="n">
         <v>1.5</v>
@@ -57651,7 +56739,7 @@
         <v>3.19</v>
       </c>
       <c r="DO125" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -57818,16 +56906,8 @@
       <c r="Z126" t="n">
         <v>62</v>
       </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>Parque Luis Méndez Piana</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>Avenida Ramón V. Benzano, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="n">
         <v>5</v>
       </c>
@@ -58069,7 +57149,7 @@
         <v>2</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DF126" t="n">
         <v>1.86</v>
@@ -58099,7 +57179,7 @@
         <v>2.31</v>
       </c>
       <c r="DO126" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -58266,16 +57346,8 @@
       <c r="Z127" t="n">
         <v>59</v>
       </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>Parque Osvaldo Roberto</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>Avenida Millán 4712 entre Avenida Sayago y Vedia, Barrio Sayago, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="n">
         <v>4</v>
       </c>
@@ -58514,7 +57586,7 @@
         <v>69</v>
       </c>
       <c r="DD127" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DE127" t="n">
         <v>1.11</v>
@@ -58547,7 +57619,7 @@
         <v>2.97</v>
       </c>
       <c r="DO127" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -58714,16 +57786,8 @@
       <c r="Z128" t="n">
         <v>48</v>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="n">
         <v>2</v>
       </c>
@@ -58962,10 +58026,10 @@
         <v>93</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE128" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF128" t="n">
         <v>1.63</v>
@@ -58995,7 +58059,7 @@
         <v>2.88</v>
       </c>
       <c r="DO128" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP128" t="b">
         <v>0</v>
@@ -59162,16 +58226,8 @@
       <c r="Z129" t="n">
         <v>49</v>
       </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>Estadio Domingo Burgueño Miguel</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>, Maldonado</t>
-        </is>
-      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="n">
         <v>6</v>
       </c>
@@ -59410,7 +58466,7 @@
         <v>75</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE129" t="n">
         <v>0.89</v>
@@ -59443,7 +58499,7 @@
         <v>2.5</v>
       </c>
       <c r="DO129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -59626,16 +58682,8 @@
       <c r="Z130" t="n">
         <v>53</v>
       </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="n">
         <v>6</v>
       </c>
@@ -59907,7 +58955,7 @@
         <v>2.96</v>
       </c>
       <c r="DO130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP130" t="b">
         <v>0</v>
@@ -60066,16 +59114,8 @@
       <c r="Z131" t="n">
         <v>61</v>
       </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>Parque Abraham Paladino</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>Avenida Emilio Romero, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="n">
         <v>7</v>
       </c>
@@ -60317,7 +59357,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DF131" t="n">
         <v>0.63</v>
@@ -60347,7 +59387,7 @@
         <v>2.71</v>
       </c>
       <c r="DO131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -60507,16 +59547,16 @@
         <v>1</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W132" t="n">
         <v>2</v>
@@ -60525,21 +59565,13 @@
         <v>9</v>
       </c>
       <c r="Y132" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Z132" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>Estadio Municipal Arquitecto Antonio Eleuterio Ubilla</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>Calle José Batlle y Ordóñez 695 esc. 101, Melo</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="n">
         <v>1</v>
       </c>
@@ -60688,13 +59720,13 @@
         <v>97</v>
       </c>
       <c r="BZ132" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="CA132" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="CB132" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="CC132" t="n">
         <v>0</v>
@@ -60778,7 +59810,7 @@
         <v>72</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE132" t="n">
         <v>0.88</v>
@@ -60811,7 +59843,7 @@
         <v>2.22</v>
       </c>
       <c r="DO132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -60994,16 +60026,8 @@
       <c r="Z133" t="n">
         <v>34</v>
       </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>Estadio Gran Parque Central</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>Avenida Carlos Anaya 2900 y Tristán Azambuya, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="n">
         <v>6</v>
       </c>
@@ -61275,7 +60299,7 @@
         <v>3.07</v>
       </c>
       <c r="DO133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -61395,10 +60419,10 @@
         <v>5</v>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M134" t="n">
         <v>4</v>
@@ -61419,39 +60443,31 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T134" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U134" t="n">
+        <v>15</v>
+      </c>
+      <c r="V134" t="n">
         <v>6</v>
       </c>
-      <c r="V134" t="n">
-        <v>4</v>
-      </c>
       <c r="W134" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="X134" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="Y134" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z134" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>Estadio Monumental Luis Tróccoli</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Santín Carlos Rossi 4702 esq. Camina La Paloma, Barrio La Paloma, Montevideo</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="n">
         <v>4</v>
       </c>
@@ -61600,13 +60616,13 @@
         <v>83</v>
       </c>
       <c r="BZ134" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="CA134" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="CB134" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="CC134" t="n">
         <v>0</v>
@@ -61651,31 +60667,31 @@
         <v>0</v>
       </c>
       <c r="CQ134" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CS134" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CT134" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CV134" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW134" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY134" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ134" t="n">
         <v>32</v>
@@ -61693,7 +60709,7 @@
         <v>1.33</v>
       </c>
       <c r="DE134" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF134" t="n">
         <v>1.13</v>
@@ -61723,7 +60739,7 @@
         <v>2.65</v>
       </c>
       <c r="DO134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -61898,16 +60914,8 @@
       <c r="Z135" t="n">
         <v>51</v>
       </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>Parque Alfredo Víctor Viera</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>Avenida Buschental entre Atilio Pelossi y Lucas Obes, Barrio Prado, Montevideo</t>
-        </is>
-      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="n">
         <v>1</v>
       </c>
@@ -62179,7 +61187,7 @@
         <v>2.77</v>
       </c>
       <c r="DO135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -62323,39 +61331,31 @@
         <v>3</v>
       </c>
       <c r="S136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T136" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U136" t="n">
+        <v>15</v>
+      </c>
+      <c r="V136" t="n">
         <v>12</v>
       </c>
-      <c r="V136" t="n">
-        <v>6</v>
-      </c>
       <c r="W136" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="X136" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="Y136" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z136" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>Estadio Luis Franzini</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>Avenida Dr. Julio Herrera y Reissig 687 esq. Avenida Sarmiento, Parque Rodó, Montevideo</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="n">
         <v>2</v>
       </c>
@@ -62504,13 +61504,13 @@
         <v>84</v>
       </c>
       <c r="BZ136" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="CB136" t="n">
-        <v>2.47</v>
+        <v>3.03</v>
       </c>
       <c r="CC136" t="n">
         <v>0</v>
@@ -62555,31 +61555,31 @@
         <v>0</v>
       </c>
       <c r="CQ136" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR136" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="CS136" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="CT136" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU136" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CV136" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW136" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX136" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY136" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ136" t="n">
         <v>29</v>
@@ -62627,7 +61627,7 @@
         <v>3.43</v>
       </c>
       <c r="DO136" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -62690,6 +61690,3574 @@
       <c r="EJ136" t="inlineStr"/>
       <c r="EK136" t="inlineStr"/>
       <c r="EL136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>46171.9375</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>5</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>6</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" t="n">
+        <v>2</v>
+      </c>
+      <c r="S137" t="n">
+        <v>12</v>
+      </c>
+      <c r="T137" t="n">
+        <v>7</v>
+      </c>
+      <c r="U137" t="n">
+        <v>17</v>
+      </c>
+      <c r="V137" t="n">
+        <v>9</v>
+      </c>
+      <c r="W137" t="n">
+        <v>9</v>
+      </c>
+      <c r="X137" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>4371</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>3</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW137" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX137" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>4.91</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr"/>
+      <c r="EH137" t="inlineStr"/>
+      <c r="EI137" t="inlineStr"/>
+      <c r="EJ137" t="inlineStr"/>
+      <c r="EK137" t="inlineStr"/>
+      <c r="EL137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>46172.54166666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>10</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>11</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>23</v>
+      </c>
+      <c r="T138" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" t="n">
+        <v>24</v>
+      </c>
+      <c r="V138" t="n">
+        <v>7</v>
+      </c>
+      <c r="W138" t="n">
+        <v>12</v>
+      </c>
+      <c r="X138" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>94</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>18</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>28</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX138" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EF138" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr"/>
+      <c r="EH138" t="inlineStr"/>
+      <c r="EI138" t="inlineStr"/>
+      <c r="EJ138" t="inlineStr"/>
+      <c r="EK138" t="inlineStr"/>
+      <c r="EL138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>46172.75</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>3</v>
+      </c>
+      <c r="K139" t="n">
+        <v>7</v>
+      </c>
+      <c r="L139" t="n">
+        <v>10</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>3</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6</v>
+      </c>
+      <c r="S139" t="n">
+        <v>3</v>
+      </c>
+      <c r="T139" t="n">
+        <v>5</v>
+      </c>
+      <c r="U139" t="n">
+        <v>6</v>
+      </c>
+      <c r="V139" t="n">
+        <v>11</v>
+      </c>
+      <c r="W139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>4378</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>73</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW139" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX139" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EE139" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EF139" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EG139" t="inlineStr"/>
+      <c r="EH139" t="inlineStr"/>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL139" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>4</v>
+      </c>
+      <c r="K140" t="n">
+        <v>11</v>
+      </c>
+      <c r="L140" t="n">
+        <v>15</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="n">
+        <v>2</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>3</v>
+      </c>
+      <c r="R140" t="n">
+        <v>5</v>
+      </c>
+      <c r="S140" t="n">
+        <v>2</v>
+      </c>
+      <c r="T140" t="n">
+        <v>6</v>
+      </c>
+      <c r="U140" t="n">
+        <v>5</v>
+      </c>
+      <c r="V140" t="n">
+        <v>11</v>
+      </c>
+      <c r="W140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>82</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="DX140" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EG140" t="inlineStr"/>
+      <c r="EH140" t="inlineStr"/>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>3</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>46173.75</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>5</v>
+      </c>
+      <c r="I141" t="n">
+        <v>7</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>6</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6</v>
+      </c>
+      <c r="M141" t="n">
+        <v>4</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>2</v>
+      </c>
+      <c r="R141" t="n">
+        <v>9</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>2</v>
+      </c>
+      <c r="U141" t="n">
+        <v>2</v>
+      </c>
+      <c r="V141" t="n">
+        <v>11</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>4350</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW141" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DX141" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="ED141" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EE141" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF141" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr"/>
+      <c r="EI141" t="inlineStr"/>
+      <c r="EJ141" t="inlineStr"/>
+      <c r="EK141" t="inlineStr"/>
+      <c r="EL141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="n">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>3</v>
+      </c>
+      <c r="J142" t="n">
+        <v>7</v>
+      </c>
+      <c r="K142" t="n">
+        <v>7</v>
+      </c>
+      <c r="L142" t="n">
+        <v>14</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>4</v>
+      </c>
+      <c r="R142" t="n">
+        <v>4</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="n">
+        <v>12</v>
+      </c>
+      <c r="U142" t="n">
+        <v>9</v>
+      </c>
+      <c r="V142" t="n">
+        <v>16</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>4373</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>76</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>76</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>65</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>89</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DX142" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EC142" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EE142" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF142" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr"/>
+      <c r="EI142" t="inlineStr"/>
+      <c r="EJ142" t="inlineStr"/>
+      <c r="EK142" t="inlineStr"/>
+      <c r="EL142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Liverpool FC Montevideo</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="n">
+        <v>46174.75</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="n">
+        <v>5</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>5</v>
+      </c>
+      <c r="N143" t="n">
+        <v>6</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>5</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>4</v>
+      </c>
+      <c r="U143" t="n">
+        <v>10</v>
+      </c>
+      <c r="V143" t="n">
+        <v>10</v>
+      </c>
+      <c r="W143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>4357</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>39</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW143" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX143" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EC143" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EE143" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EF143" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="EG143" t="inlineStr"/>
+      <c r="EH143" t="inlineStr"/>
+      <c r="EI143" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EL143" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="n">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>6</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3</v>
+      </c>
+      <c r="L144" t="n">
+        <v>9</v>
+      </c>
+      <c r="M144" t="n">
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>3</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>3</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2</v>
+      </c>
+      <c r="S144" t="n">
+        <v>4</v>
+      </c>
+      <c r="T144" t="n">
+        <v>3</v>
+      </c>
+      <c r="U144" t="n">
+        <v>7</v>
+      </c>
+      <c r="V144" t="n">
+        <v>5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>4377</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV144" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW144" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>167</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK144" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL144" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DM144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN144" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DO144" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP144" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV144" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW144" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="DX144" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="DY144" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ144" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EA144" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EB144" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC144" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr"/>
+      <c r="EH144" t="inlineStr"/>
+      <c r="EI144" t="inlineStr"/>
+      <c r="EJ144" t="inlineStr"/>
+      <c r="EK144" t="inlineStr"/>
+      <c r="EL144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
+++ b/data/matches/leagues/Uruguay_Primera_División_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL144" headerRowCount="1">
-  <autoFilter ref="A1:EL144"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL145" headerRowCount="1">
+  <autoFilter ref="A1:EL145"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL144"/>
+  <dimension ref="A1:EL145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE3" t="n">
         <v>1.22</v>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5305,7 +5305,7 @@
         <v>1.28</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -7115,7 +7115,7 @@
         <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -9843,7 +9843,7 @@
         <v>2.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11146,7 +11146,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE23" t="n">
         <v>1.61</v>
@@ -13851,7 +13851,7 @@
         <v>1.86</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14285,7 +14285,7 @@
         <v>1.67</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -16098,7 +16098,7 @@
         <v>88</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE34" t="n">
         <v>2</v>
@@ -17011,7 +17011,7 @@
         <v>2.3</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19661,7 +19661,7 @@
         <v>1.56</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF42" t="n">
         <v>1.4</v>
@@ -25078,7 +25078,7 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE54" t="n">
         <v>1.06</v>
@@ -25111,7 +25111,7 @@
         <v>2.47</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -28305,7 +28305,7 @@
         <v>1.61</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF61" t="n">
         <v>1.14</v>
@@ -30155,7 +30155,7 @@
         <v>2.62</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -30578,7 +30578,7 @@
         <v>57</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE66" t="n">
         <v>0.72</v>
@@ -32367,7 +32367,7 @@
         <v>2.45</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34113,7 +34113,7 @@
         <v>1.11</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF74" t="n">
         <v>0.89</v>
@@ -35487,7 +35487,7 @@
         <v>2.56</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -39527,7 +39527,7 @@
         <v>2.5</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40366,7 +40366,7 @@
         <v>75</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE88" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         <v>0.72</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF91" t="n">
         <v>0.64</v>
@@ -43055,7 +43055,7 @@
         <v>2.66</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46175,7 +46175,7 @@
         <v>2.81</v>
       </c>
       <c r="DO101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47462,7 +47462,7 @@
         <v>83</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE104" t="n">
         <v>1.83</v>
@@ -48377,7 +48377,7 @@
         <v>1.06</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DF106" t="n">
         <v>0.6899999999999999</v>
@@ -49271,7 +49271,7 @@
         <v>2.57</v>
       </c>
       <c r="DO108" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51894,7 +51894,7 @@
         <v>75</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DE114" t="n">
         <v>1.33</v>
@@ -52367,7 +52367,7 @@
         <v>2.54</v>
       </c>
       <c r="DO115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -58469,7 +58469,7 @@
         <v>2.67</v>
       </c>
       <c r="DE129" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF129" t="n">
         <v>2.57</v>
@@ -58499,7 +58499,7 @@
         <v>2.5</v>
       </c>
       <c r="DO129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -61154,7 +61154,7 @@
         <v>75</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DE135" t="n">
         <v>1.33</v>
@@ -62931,7 +62931,7 @@
         <v>2.57</v>
       </c>
       <c r="DO139" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -64427,28 +64427,28 @@
         <v>6</v>
       </c>
       <c r="S143" t="n">
+        <v>8</v>
+      </c>
+      <c r="T143" t="n">
         <v>5</v>
       </c>
-      <c r="T143" t="n">
-        <v>4</v>
-      </c>
       <c r="U143" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V143" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W143" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="X143" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="Y143" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Z143" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AA143" t="inlineStr"/>
       <c r="AB143" t="inlineStr"/>
@@ -64600,13 +64600,13 @@
         <v>87</v>
       </c>
       <c r="BZ143" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="CA143" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="CB143" t="n">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="CC143" t="n">
         <v>0</v>
@@ -64651,31 +64651,31 @@
         <v>0</v>
       </c>
       <c r="CQ143" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR143" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CS143" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CT143" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU143" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CV143" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CW143" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX143" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CY143" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ143" t="n">
         <v>39</v>
@@ -64883,28 +64883,28 @@
         <v>2</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="T144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="V144" t="n">
+        <v>8</v>
+      </c>
+      <c r="W144" t="n">
+        <v>10</v>
+      </c>
+      <c r="X144" t="n">
         <v>5</v>
       </c>
-      <c r="W144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X144" t="n">
-        <v>-1</v>
-      </c>
       <c r="Y144" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Z144" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
@@ -65056,13 +65056,13 @@
         <v>106</v>
       </c>
       <c r="BZ144" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="CB144" t="n">
-        <v>2.11</v>
+        <v>3.22</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>
@@ -65107,31 +65107,31 @@
         <v>0</v>
       </c>
       <c r="CQ144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="CS144" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CT144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CU144" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CV144" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CW144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX144" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY144" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CZ144" t="n">
         <v>62</v>
@@ -65258,6 +65258,430 @@
       <c r="EJ144" t="inlineStr"/>
       <c r="EK144" t="inlineStr"/>
       <c r="EL144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Uruguay_Primera_División_2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="n">
+        <v>46178.91666666666</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>8</v>
+      </c>
+      <c r="L145" t="n">
+        <v>10</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6</v>
+      </c>
+      <c r="S145" t="n">
+        <v>7</v>
+      </c>
+      <c r="T145" t="n">
+        <v>6</v>
+      </c>
+      <c r="U145" t="n">
+        <v>8</v>
+      </c>
+      <c r="V145" t="n">
+        <v>12</v>
+      </c>
+      <c r="W145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CV145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ145" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA145" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB145" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC145" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD145" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE145" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF145" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG145" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DH145" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DI145" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ145" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK145" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM145" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN145" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO145" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV145" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW145" t="inlineStr"/>
+      <c r="DX145" t="inlineStr"/>
+      <c r="DY145" t="inlineStr"/>
+      <c r="DZ145" t="inlineStr"/>
+      <c r="EA145" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EB145" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EC145" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="ED145" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EE145" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EF145" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="EG145" t="inlineStr"/>
+      <c r="EH145" t="inlineStr"/>
+      <c r="EI145" t="inlineStr"/>
+      <c r="EJ145" t="inlineStr"/>
+      <c r="EK145" t="inlineStr"/>
+      <c r="EL145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
